--- a/data_raw/precios_hacienda_inac.xlsx
+++ b/data_raw/precios_hacienda_inac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Usuarios\PUBLICO\PDF DE HACIENDA PARA WEB\Hacienda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GIF\Análisis sectorial\Indicadores y Precios\Precios Hacienda\SERIES DE PRECIOS SEMANALES Y MENSUALES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25FCC11D-6075-430A-BFC1-36950A2873E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8118934B-1BFB-4B1D-82E6-89B0432E28AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HACIENDA" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="36">
   <si>
     <t>Ene</t>
   </si>
@@ -1440,7 +1440,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$339</c:f>
+              <c:f>HACIENDA!$E$340</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1815,7 +1815,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$338</c:f>
+              <c:f>HACIENDA!$A$339</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1889,12 +1889,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$338</c:f>
+              <c:f>HACIENDA!$E$339</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.37</c:v>
+                  <c:v>5.6180000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2078,7 +2078,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -2191,7 +2191,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$A$278</c15:sqref>
@@ -2218,7 +2218,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -2268,7 +2268,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$E$278:$E$289</c15:sqref>
@@ -2318,7 +2318,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-5403-4D48-BC15-EEB93EEEC2DD}"/>
                   </c:ext>
@@ -3001,7 +3001,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$338</c:f>
+              <c:f>HACIENDA!$A$339</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3075,12 +3075,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$H$338</c:f>
+              <c:f>HACIENDA!$H$339</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4.9130000000000003</c:v>
+                  <c:v>5.2309999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3250,7 +3250,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -3363,7 +3363,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$A$278</c15:sqref>
@@ -3390,7 +3390,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -3440,7 +3440,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$H$278:$H$289</c15:sqref>
@@ -3490,7 +3490,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-21ED-4E38-948A-6D9CCCEDEB0F}"/>
                   </c:ext>
@@ -4182,7 +4182,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$338</c:f>
+              <c:f>HACIENDA!$A$339</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4256,12 +4256,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338</c:f>
+              <c:f>HACIENDA!$J$339</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.25</c:v>
+                  <c:v>5.52</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4431,7 +4431,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -4544,7 +4544,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$A$278</c15:sqref>
@@ -4571,7 +4571,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -4621,7 +4621,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$J$278:$J$289</c15:sqref>
@@ -4671,7 +4671,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-70AC-4DC8-874F-CAC365D27022}"/>
                   </c:ext>
@@ -5339,7 +5339,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$338</c:f>
+              <c:f>HACIENDA!$A$339</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5413,12 +5413,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338</c:f>
+              <c:f>HACIENDA!$J$339</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.25</c:v>
+                  <c:v>5.52</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5588,7 +5588,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -5714,7 +5714,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -5764,7 +5764,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$L$278:$L$289</c15:sqref>
@@ -5814,7 +5814,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-E074-4555-8623-99266DA84EFF}"/>
                   </c:ext>
@@ -6485,7 +6485,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$338</c:f>
+              <c:f>HACIENDA!$A$339</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6561,10 +6561,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$M$326:$M$338</c:f>
+              <c:f>HACIENDA!$M$326:$M$339</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>3.3580000000000001</c:v>
                 </c:pt>
@@ -6603,6 +6603,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>4.6260000000000003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.7889999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8653,21 +8656,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M338"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M339"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" hidden="1" customWidth="1"/>
-    <col min="3" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" customWidth="1"/>
-    <col min="12" max="13" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" hidden="1" customWidth="1"/>
+    <col min="3" max="5" width="11.54296875" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" customWidth="1"/>
+    <col min="7" max="9" width="11.54296875" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" customWidth="1"/>
+    <col min="12" max="13" width="11.54296875" customWidth="1"/>
     <col min="14" max="14" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
@@ -8683,7 +8686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
       <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
@@ -8697,44 +8700,44 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D4" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D6" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C7" s="19"/>
       <c r="D7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="19"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D8" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D9" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
         <v>22</v>
       </c>
@@ -8767,7 +8770,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="27.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="27.5" x14ac:dyDescent="0.35">
       <c r="A11" s="20"/>
       <c r="B11" s="16" t="s">
         <v>35</v>
@@ -8804,7 +8807,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>1998</v>
       </c>
@@ -8827,7 +8830,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>1998</v>
       </c>
@@ -8850,7 +8853,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>1999</v>
       </c>
@@ -8875,7 +8878,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>1999</v>
       </c>
@@ -8900,7 +8903,7 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>1999</v>
       </c>
@@ -8925,7 +8928,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>1999</v>
       </c>
@@ -8950,7 +8953,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>1999</v>
       </c>
@@ -8975,7 +8978,7 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>1999</v>
       </c>
@@ -9000,7 +9003,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>1999</v>
       </c>
@@ -9025,7 +9028,7 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>1999</v>
       </c>
@@ -9050,7 +9053,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>1999</v>
       </c>
@@ -9075,7 +9078,7 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>1999</v>
       </c>
@@ -9100,7 +9103,7 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>1999</v>
       </c>
@@ -9125,7 +9128,7 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>1999</v>
       </c>
@@ -9150,7 +9153,7 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2000</v>
       </c>
@@ -9175,7 +9178,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -9200,7 +9203,7 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2000</v>
       </c>
@@ -9225,7 +9228,7 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2000</v>
       </c>
@@ -9250,7 +9253,7 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2000</v>
       </c>
@@ -9275,7 +9278,7 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2000</v>
       </c>
@@ -9300,7 +9303,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2000</v>
       </c>
@@ -9325,7 +9328,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2000</v>
       </c>
@@ -9350,7 +9353,7 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2000</v>
       </c>
@@ -9375,7 +9378,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2000</v>
       </c>
@@ -9400,7 +9403,7 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2000</v>
       </c>
@@ -9425,7 +9428,7 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2000</v>
       </c>
@@ -9450,7 +9453,7 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2001</v>
       </c>
@@ -9475,7 +9478,7 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2001</v>
       </c>
@@ -9500,7 +9503,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2001</v>
       </c>
@@ -9525,7 +9528,7 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2001</v>
       </c>
@@ -9550,7 +9553,7 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>2001</v>
       </c>
@@ -9575,7 +9578,7 @@
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>2001</v>
       </c>
@@ -9600,7 +9603,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>2001</v>
       </c>
@@ -9625,7 +9628,7 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>2001</v>
       </c>
@@ -9650,7 +9653,7 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>2001</v>
       </c>
@@ -9675,7 +9678,7 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>2001</v>
       </c>
@@ -9700,7 +9703,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>2001</v>
       </c>
@@ -9725,7 +9728,7 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>2001</v>
       </c>
@@ -9750,7 +9753,7 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>2002</v>
       </c>
@@ -9775,7 +9778,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>2002</v>
       </c>
@@ -9800,7 +9803,7 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>2002</v>
       </c>
@@ -9825,7 +9828,7 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>2002</v>
       </c>
@@ -9850,7 +9853,7 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>2002</v>
       </c>
@@ -9875,7 +9878,7 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2002</v>
       </c>
@@ -9900,7 +9903,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2002</v>
       </c>
@@ -9925,7 +9928,7 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2002</v>
       </c>
@@ -9950,7 +9953,7 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2002</v>
       </c>
@@ -9975,7 +9978,7 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2002</v>
       </c>
@@ -10000,7 +10003,7 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2002</v>
       </c>
@@ -10025,7 +10028,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2002</v>
       </c>
@@ -10050,7 +10053,7 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2003</v>
       </c>
@@ -10081,7 +10084,7 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2003</v>
       </c>
@@ -10112,7 +10115,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2003</v>
       </c>
@@ -10143,7 +10146,7 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2003</v>
       </c>
@@ -10174,7 +10177,7 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2003</v>
       </c>
@@ -10205,7 +10208,7 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2003</v>
       </c>
@@ -10236,7 +10239,7 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2003</v>
       </c>
@@ -10267,7 +10270,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2003</v>
       </c>
@@ -10298,7 +10301,7 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>2003</v>
       </c>
@@ -10329,7 +10332,7 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2003</v>
       </c>
@@ -10360,7 +10363,7 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2003</v>
       </c>
@@ -10391,7 +10394,7 @@
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>2003</v>
       </c>
@@ -10422,7 +10425,7 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>2004</v>
       </c>
@@ -10453,7 +10456,7 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2004</v>
       </c>
@@ -10484,7 +10487,7 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>2004</v>
       </c>
@@ -10515,7 +10518,7 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2004</v>
       </c>
@@ -10546,7 +10549,7 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2004</v>
       </c>
@@ -10577,7 +10580,7 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2004</v>
       </c>
@@ -10608,7 +10611,7 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2004</v>
       </c>
@@ -10639,7 +10642,7 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2004</v>
       </c>
@@ -10670,7 +10673,7 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2004</v>
       </c>
@@ -10701,7 +10704,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>2004</v>
       </c>
@@ -10732,7 +10735,7 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2004</v>
       </c>
@@ -10763,7 +10766,7 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2004</v>
       </c>
@@ -10794,7 +10797,7 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2005</v>
       </c>
@@ -10825,7 +10828,7 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2005</v>
       </c>
@@ -10856,7 +10859,7 @@
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2005</v>
       </c>
@@ -10887,7 +10890,7 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>2005</v>
       </c>
@@ -10918,7 +10921,7 @@
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2005</v>
       </c>
@@ -10949,7 +10952,7 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2005</v>
       </c>
@@ -10980,7 +10983,7 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>2005</v>
       </c>
@@ -11011,7 +11014,7 @@
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>2005</v>
       </c>
@@ -11042,7 +11045,7 @@
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>2005</v>
       </c>
@@ -11073,7 +11076,7 @@
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2005</v>
       </c>
@@ -11104,7 +11107,7 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2005</v>
       </c>
@@ -11135,7 +11138,7 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>2005</v>
       </c>
@@ -11166,7 +11169,7 @@
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2006</v>
       </c>
@@ -11197,7 +11200,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2006</v>
       </c>
@@ -11228,7 +11231,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2006</v>
       </c>
@@ -11259,7 +11262,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2006</v>
       </c>
@@ -11290,7 +11293,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2006</v>
       </c>
@@ -11321,7 +11324,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2006</v>
       </c>
@@ -11352,7 +11355,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>2006</v>
       </c>
@@ -11383,7 +11386,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2006</v>
       </c>
@@ -11414,7 +11417,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>2006</v>
       </c>
@@ -11445,7 +11448,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>2006</v>
       </c>
@@ -11476,7 +11479,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2006</v>
       </c>
@@ -11507,7 +11510,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>2006</v>
       </c>
@@ -11538,7 +11541,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>2007</v>
       </c>
@@ -11569,7 +11572,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2007</v>
       </c>
@@ -11600,7 +11603,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>2007</v>
       </c>
@@ -11631,7 +11634,7 @@
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2007</v>
       </c>
@@ -11662,7 +11665,7 @@
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2007</v>
       </c>
@@ -11693,7 +11696,7 @@
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>2007</v>
       </c>
@@ -11724,7 +11727,7 @@
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2007</v>
       </c>
@@ -11755,7 +11758,7 @@
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>2007</v>
       </c>
@@ -11786,7 +11789,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>2007</v>
       </c>
@@ -11817,7 +11820,7 @@
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>2007</v>
       </c>
@@ -11848,7 +11851,7 @@
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>2007</v>
       </c>
@@ -11879,7 +11882,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>2007</v>
       </c>
@@ -11910,7 +11913,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>2008</v>
       </c>
@@ -11941,7 +11944,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>2008</v>
       </c>
@@ -11972,7 +11975,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>2008</v>
       </c>
@@ -12003,7 +12006,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>2008</v>
       </c>
@@ -12034,7 +12037,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>2008</v>
       </c>
@@ -12065,7 +12068,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>2008</v>
       </c>
@@ -12096,7 +12099,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>2008</v>
       </c>
@@ -12127,7 +12130,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>2008</v>
       </c>
@@ -12158,7 +12161,7 @@
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>2008</v>
       </c>
@@ -12189,7 +12192,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>2008</v>
       </c>
@@ -12220,7 +12223,7 @@
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>2008</v>
       </c>
@@ -12251,7 +12254,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>2008</v>
       </c>
@@ -12282,7 +12285,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>2009</v>
       </c>
@@ -12313,7 +12316,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>2009</v>
       </c>
@@ -12344,7 +12347,7 @@
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>2009</v>
       </c>
@@ -12375,7 +12378,7 @@
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>2009</v>
       </c>
@@ -12406,7 +12409,7 @@
       <c r="L137" s="3"/>
       <c r="M137" s="3"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>2009</v>
       </c>
@@ -12437,7 +12440,7 @@
       <c r="L138" s="3"/>
       <c r="M138" s="3"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>2009</v>
       </c>
@@ -12468,7 +12471,7 @@
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>2009</v>
       </c>
@@ -12499,7 +12502,7 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>2009</v>
       </c>
@@ -12530,7 +12533,7 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>2009</v>
       </c>
@@ -12561,7 +12564,7 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>2009</v>
       </c>
@@ -12592,7 +12595,7 @@
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>2009</v>
       </c>
@@ -12623,7 +12626,7 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>2009</v>
       </c>
@@ -12654,7 +12657,7 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>2010</v>
       </c>
@@ -12685,7 +12688,7 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>2010</v>
       </c>
@@ -12716,7 +12719,7 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>2010</v>
       </c>
@@ -12747,7 +12750,7 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>2010</v>
       </c>
@@ -12778,7 +12781,7 @@
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>2010</v>
       </c>
@@ -12809,7 +12812,7 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>2010</v>
       </c>
@@ -12840,7 +12843,7 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>2010</v>
       </c>
@@ -12871,7 +12874,7 @@
       <c r="L152" s="3"/>
       <c r="M152" s="3"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>2010</v>
       </c>
@@ -12902,7 +12905,7 @@
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>2010</v>
       </c>
@@ -12933,7 +12936,7 @@
       <c r="L154" s="3"/>
       <c r="M154" s="3"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>2010</v>
       </c>
@@ -12964,7 +12967,7 @@
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>2010</v>
       </c>
@@ -12995,7 +12998,7 @@
       <c r="L156" s="3"/>
       <c r="M156" s="3"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>2010</v>
       </c>
@@ -13026,7 +13029,7 @@
       <c r="L157" s="3"/>
       <c r="M157" s="3"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>2011</v>
       </c>
@@ -13059,7 +13062,7 @@
       </c>
       <c r="M158" s="3"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>2011</v>
       </c>
@@ -13092,7 +13095,7 @@
       </c>
       <c r="M159" s="3"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>2011</v>
       </c>
@@ -13125,7 +13128,7 @@
       </c>
       <c r="M160" s="3"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>2011</v>
       </c>
@@ -13158,7 +13161,7 @@
       </c>
       <c r="M161" s="3"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>2011</v>
       </c>
@@ -13191,7 +13194,7 @@
       </c>
       <c r="M162" s="3"/>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>2011</v>
       </c>
@@ -13224,7 +13227,7 @@
       </c>
       <c r="M163" s="3"/>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>2011</v>
       </c>
@@ -13257,7 +13260,7 @@
       </c>
       <c r="M164" s="3"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>2011</v>
       </c>
@@ -13290,7 +13293,7 @@
       </c>
       <c r="M165" s="3"/>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>2011</v>
       </c>
@@ -13323,7 +13326,7 @@
       </c>
       <c r="M166" s="3"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>2011</v>
       </c>
@@ -13356,7 +13359,7 @@
       </c>
       <c r="M167" s="3"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>2011</v>
       </c>
@@ -13389,7 +13392,7 @@
       </c>
       <c r="M168" s="3"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>2011</v>
       </c>
@@ -13422,7 +13425,7 @@
       </c>
       <c r="M169" s="3"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>2012</v>
       </c>
@@ -13455,7 +13458,7 @@
       </c>
       <c r="M170" s="3"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>2012</v>
       </c>
@@ -13488,7 +13491,7 @@
       </c>
       <c r="M171" s="3"/>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>2012</v>
       </c>
@@ -13521,7 +13524,7 @@
       </c>
       <c r="M172" s="3"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>2012</v>
       </c>
@@ -13554,7 +13557,7 @@
       </c>
       <c r="M173" s="3"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>2012</v>
       </c>
@@ -13587,7 +13590,7 @@
       </c>
       <c r="M174" s="3"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>2012</v>
       </c>
@@ -13620,7 +13623,7 @@
       </c>
       <c r="M175" s="3"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>2012</v>
       </c>
@@ -13653,7 +13656,7 @@
       </c>
       <c r="M176" s="3"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>2012</v>
       </c>
@@ -13686,7 +13689,7 @@
       </c>
       <c r="M177" s="3"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>2012</v>
       </c>
@@ -13719,7 +13722,7 @@
       </c>
       <c r="M178" s="3"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>2012</v>
       </c>
@@ -13752,7 +13755,7 @@
       </c>
       <c r="M179" s="3"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>2012</v>
       </c>
@@ -13785,7 +13788,7 @@
       </c>
       <c r="M180" s="3"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>2012</v>
       </c>
@@ -13818,7 +13821,7 @@
       </c>
       <c r="M181" s="3"/>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>2013</v>
       </c>
@@ -13851,7 +13854,7 @@
       </c>
       <c r="M182" s="3"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>2013</v>
       </c>
@@ -13884,7 +13887,7 @@
       </c>
       <c r="M183" s="3"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>2013</v>
       </c>
@@ -13917,7 +13920,7 @@
       </c>
       <c r="M184" s="3"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>2013</v>
       </c>
@@ -13950,7 +13953,7 @@
       </c>
       <c r="M185" s="3"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>2013</v>
       </c>
@@ -13983,7 +13986,7 @@
       </c>
       <c r="M186" s="3"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>2013</v>
       </c>
@@ -14016,7 +14019,7 @@
       </c>
       <c r="M187" s="3"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>2013</v>
       </c>
@@ -14049,7 +14052,7 @@
       </c>
       <c r="M188" s="3"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>2013</v>
       </c>
@@ -14082,7 +14085,7 @@
       </c>
       <c r="M189" s="3"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>2013</v>
       </c>
@@ -14115,7 +14118,7 @@
       </c>
       <c r="M190" s="3"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>2013</v>
       </c>
@@ -14148,7 +14151,7 @@
       </c>
       <c r="M191" s="3"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>2013</v>
       </c>
@@ -14181,7 +14184,7 @@
       </c>
       <c r="M192" s="3"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>2013</v>
       </c>
@@ -14214,7 +14217,7 @@
       </c>
       <c r="M193" s="3"/>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>2014</v>
       </c>
@@ -14247,7 +14250,7 @@
       </c>
       <c r="M194" s="3"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>2014</v>
       </c>
@@ -14280,7 +14283,7 @@
       </c>
       <c r="M195" s="3"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>2014</v>
       </c>
@@ -14313,7 +14316,7 @@
       </c>
       <c r="M196" s="3"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>2014</v>
       </c>
@@ -14346,7 +14349,7 @@
       </c>
       <c r="M197" s="3"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>2014</v>
       </c>
@@ -14379,7 +14382,7 @@
       </c>
       <c r="M198" s="3"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>2014</v>
       </c>
@@ -14412,7 +14415,7 @@
       </c>
       <c r="M199" s="3"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>2014</v>
       </c>
@@ -14445,7 +14448,7 @@
       </c>
       <c r="M200" s="3"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>2014</v>
       </c>
@@ -14478,7 +14481,7 @@
       </c>
       <c r="M201" s="3"/>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>2014</v>
       </c>
@@ -14511,7 +14514,7 @@
       </c>
       <c r="M202" s="3"/>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>2014</v>
       </c>
@@ -14544,7 +14547,7 @@
       </c>
       <c r="M203" s="3"/>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>2014</v>
       </c>
@@ -14577,7 +14580,7 @@
       </c>
       <c r="M204" s="3"/>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>2014</v>
       </c>
@@ -14610,7 +14613,7 @@
       </c>
       <c r="M205" s="3"/>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>2015</v>
       </c>
@@ -14645,7 +14648,7 @@
       </c>
       <c r="M206" s="3"/>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>2015</v>
       </c>
@@ -14681,7 +14684,7 @@
       </c>
       <c r="M207" s="3"/>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>2015</v>
       </c>
@@ -14717,7 +14720,7 @@
       </c>
       <c r="M208" s="3"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>2015</v>
       </c>
@@ -14753,7 +14756,7 @@
       </c>
       <c r="M209" s="3"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>2015</v>
       </c>
@@ -14789,7 +14792,7 @@
       </c>
       <c r="M210" s="3"/>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>2015</v>
       </c>
@@ -14825,7 +14828,7 @@
       </c>
       <c r="M211" s="3"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>2015</v>
       </c>
@@ -14861,7 +14864,7 @@
       </c>
       <c r="M212" s="3"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>2015</v>
       </c>
@@ -14897,7 +14900,7 @@
       </c>
       <c r="M213" s="3"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>2015</v>
       </c>
@@ -14933,7 +14936,7 @@
       </c>
       <c r="M214" s="3"/>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>2015</v>
       </c>
@@ -14969,7 +14972,7 @@
       </c>
       <c r="M215" s="3"/>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>2015</v>
       </c>
@@ -15005,7 +15008,7 @@
       </c>
       <c r="M216" s="3"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>2015</v>
       </c>
@@ -15041,7 +15044,7 @@
       </c>
       <c r="M217" s="3"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>2016</v>
       </c>
@@ -15077,7 +15080,7 @@
       </c>
       <c r="M218" s="3"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>2016</v>
       </c>
@@ -15113,7 +15116,7 @@
       </c>
       <c r="M219" s="3"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>2016</v>
       </c>
@@ -15149,7 +15152,7 @@
       </c>
       <c r="M220" s="3"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>2016</v>
       </c>
@@ -15185,7 +15188,7 @@
       </c>
       <c r="M221" s="3"/>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>2016</v>
       </c>
@@ -15221,7 +15224,7 @@
       </c>
       <c r="M222" s="3"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>2016</v>
       </c>
@@ -15257,7 +15260,7 @@
       </c>
       <c r="M223" s="3"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>2016</v>
       </c>
@@ -15293,7 +15296,7 @@
       </c>
       <c r="M224" s="3"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>2016</v>
       </c>
@@ -15329,7 +15332,7 @@
       </c>
       <c r="M225" s="3"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>2016</v>
       </c>
@@ -15365,7 +15368,7 @@
       </c>
       <c r="M226" s="3"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>2016</v>
       </c>
@@ -15401,7 +15404,7 @@
       </c>
       <c r="M227" s="3"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>2016</v>
       </c>
@@ -15437,7 +15440,7 @@
       </c>
       <c r="M228" s="3"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>2016</v>
       </c>
@@ -15473,7 +15476,7 @@
       </c>
       <c r="M229" s="3"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>2017</v>
       </c>
@@ -15515,7 +15518,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>2017</v>
       </c>
@@ -15557,7 +15560,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>2017</v>
       </c>
@@ -15599,7 +15602,7 @@
         <v>2.8039999999999998</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>2017</v>
       </c>
@@ -15641,7 +15644,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>2017</v>
       </c>
@@ -15683,7 +15686,7 @@
         <v>2.8839999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>2017</v>
       </c>
@@ -15725,7 +15728,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>2017</v>
       </c>
@@ -15767,7 +15770,7 @@
         <v>3.069</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>2017</v>
       </c>
@@ -15809,7 +15812,7 @@
         <v>3.052</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>2017</v>
       </c>
@@ -15851,7 +15854,7 @@
         <v>3.1309999999999998</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>2017</v>
       </c>
@@ -15893,7 +15896,7 @@
         <v>3.157</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>2017</v>
       </c>
@@ -15935,7 +15938,7 @@
         <v>3.1669999999999998</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>2017</v>
       </c>
@@ -15977,7 +15980,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>2018</v>
       </c>
@@ -16019,7 +16022,7 @@
         <v>2.8159999999999998</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>2018</v>
       </c>
@@ -16061,7 +16064,7 @@
         <v>2.7549999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>2018</v>
       </c>
@@ -16103,7 +16106,7 @@
         <v>2.762</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A245" s="2">
         <v>2018</v>
       </c>
@@ -16145,7 +16148,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A246" s="2">
         <v>2018</v>
       </c>
@@ -16187,7 +16190,7 @@
         <v>2.952</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A247" s="2">
         <v>2018</v>
       </c>
@@ -16229,7 +16232,7 @@
         <v>3.0350000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A248" s="2">
         <v>2018</v>
       </c>
@@ -16271,7 +16274,7 @@
         <v>3.085</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A249" s="2">
         <v>2018</v>
       </c>
@@ -16313,7 +16316,7 @@
         <v>3.1659999999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A250" s="2">
         <v>2018</v>
       </c>
@@ -16355,7 +16358,7 @@
         <v>3.0880000000000001</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A251" s="2">
         <v>2018</v>
       </c>
@@ -16397,7 +16400,7 @@
         <v>3.105</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A252" s="2">
         <v>2018</v>
       </c>
@@ -16439,7 +16442,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A253" s="2">
         <v>2018</v>
       </c>
@@ -16481,7 +16484,7 @@
         <v>2.9950229617784081</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A254" s="2">
         <v>2019</v>
       </c>
@@ -16523,7 +16526,7 @@
         <v>2.9209999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A255" s="2">
         <v>2019</v>
       </c>
@@ -16565,7 +16568,7 @@
         <v>2.9689999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A256" s="2">
         <v>2019</v>
       </c>
@@ -16607,7 +16610,7 @@
         <v>2.9430000000000001</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A257" s="2">
         <v>2019</v>
       </c>
@@ -16649,7 +16652,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A258" s="2">
         <v>2019</v>
       </c>
@@ -16691,7 +16694,7 @@
         <v>3.121</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A259" s="2">
         <v>2019</v>
       </c>
@@ -16733,7 +16736,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A260" s="2">
         <v>2019</v>
       </c>
@@ -16775,7 +16778,7 @@
         <v>3.431</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A261" s="2">
         <v>2019</v>
       </c>
@@ -16817,7 +16820,7 @@
         <v>3.4119999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2">
         <v>2019</v>
       </c>
@@ -16859,7 +16862,7 @@
         <v>3.613</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A263" s="2">
         <v>2019</v>
       </c>
@@ -16901,7 +16904,7 @@
         <v>3.827</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A264" s="2">
         <v>2019</v>
       </c>
@@ -16943,7 +16946,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A265" s="2">
         <v>2019</v>
       </c>
@@ -16985,7 +16988,7 @@
         <v>3.9329999999999998</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A266" s="2">
         <v>2020</v>
       </c>
@@ -17027,7 +17030,7 @@
         <v>3.6349999999999998</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A267" s="2">
         <v>2020</v>
       </c>
@@ -17069,7 +17072,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A268" s="2">
         <v>2020</v>
       </c>
@@ -17111,7 +17114,7 @@
         <v>3.234</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A269" s="2">
         <v>2020</v>
       </c>
@@ -17153,7 +17156,7 @@
         <v>3.202</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A270" s="2">
         <v>2020</v>
       </c>
@@ -17195,7 +17198,7 @@
         <v>3.0590000000000002</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A271" s="2">
         <v>2020</v>
       </c>
@@ -17237,7 +17240,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A272" s="2">
         <v>2020</v>
       </c>
@@ -17279,7 +17282,7 @@
         <v>3.0859999999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A273" s="2">
         <v>2020</v>
       </c>
@@ -17321,7 +17324,7 @@
         <v>3.0609999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A274" s="2">
         <v>2020</v>
       </c>
@@ -17363,7 +17366,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A275" s="2">
         <v>2020</v>
       </c>
@@ -17405,7 +17408,7 @@
         <v>3.093</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A276" s="2">
         <v>2020</v>
       </c>
@@ -17447,7 +17450,7 @@
         <v>2.9820000000000002</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2">
         <v>2020</v>
       </c>
@@ -17489,7 +17492,7 @@
         <v>2.8410000000000002</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2">
         <v>2021</v>
       </c>
@@ -17530,7 +17533,7 @@
         <v>2.8530000000000002</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2">
         <v>2021</v>
       </c>
@@ -17572,7 +17575,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2">
         <v>2021</v>
       </c>
@@ -17614,7 +17617,7 @@
         <v>3.1920000000000002</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2">
         <v>2021</v>
       </c>
@@ -17656,7 +17659,7 @@
         <v>3.3559999999999999</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2">
         <v>2021</v>
       </c>
@@ -17698,7 +17701,7 @@
         <v>3.6019999999999999</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2">
         <v>2021</v>
       </c>
@@ -17740,7 +17743,7 @@
         <v>3.8460000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2">
         <v>2021</v>
       </c>
@@ -17782,7 +17785,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2">
         <v>2021</v>
       </c>
@@ -17824,7 +17827,7 @@
         <v>4.2069999999999999</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2">
         <v>2021</v>
       </c>
@@ -17866,7 +17869,7 @@
         <v>4.3579999999999997</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2">
         <v>2021</v>
       </c>
@@ -17908,7 +17911,7 @@
         <v>4.4829999999999997</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2">
         <v>2021</v>
       </c>
@@ -17950,7 +17953,7 @@
         <v>4.3630000000000004</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2">
         <v>2021</v>
       </c>
@@ -17992,7 +17995,7 @@
         <v>3.9740000000000002</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2">
         <v>2022</v>
       </c>
@@ -18034,7 +18037,7 @@
         <v>3.6070000000000002</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2">
         <v>2022</v>
       </c>
@@ -18076,7 +18079,7 @@
         <v>3.6589999999999998</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2">
         <v>2022</v>
       </c>
@@ -18118,7 +18121,7 @@
         <v>3.964</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2">
         <v>2022</v>
       </c>
@@ -18160,7 +18163,7 @@
         <v>4.0640000000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2">
         <v>2022</v>
       </c>
@@ -18199,7 +18202,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2">
         <v>2022</v>
       </c>
@@ -18238,7 +18241,7 @@
         <v>4.1920000000000002</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2">
         <v>2022</v>
       </c>
@@ -18277,7 +18280,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2">
         <v>2022</v>
       </c>
@@ -18316,7 +18319,7 @@
         <v>4.2949999999999999</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2">
         <v>2022</v>
       </c>
@@ -18355,7 +18358,7 @@
         <v>4.0940000000000003</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2">
         <v>2022</v>
       </c>
@@ -18394,7 +18397,7 @@
         <v>3.1629999999999998</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2">
         <v>2022</v>
       </c>
@@ -18433,7 +18436,7 @@
         <v>2.6560000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2">
         <v>2022</v>
       </c>
@@ -18472,7 +18475,7 @@
         <v>2.536</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2">
         <v>2023</v>
       </c>
@@ -18511,7 +18514,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2">
         <v>2023</v>
       </c>
@@ -18550,7 +18553,7 @@
         <v>2.7469999999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2">
         <v>2023</v>
       </c>
@@ -18589,7 +18592,7 @@
         <v>2.9980000000000002</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2">
         <v>2023</v>
       </c>
@@ -18628,7 +18631,7 @@
         <v>3.1240000000000001</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2">
         <v>2023</v>
       </c>
@@ -18667,7 +18670,7 @@
         <v>2.8090000000000002</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2">
         <v>2023</v>
       </c>
@@ -18706,7 +18709,7 @@
         <v>2.5579999999999998</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2">
         <v>2023</v>
       </c>
@@ -18745,7 +18748,7 @@
         <v>2.532</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2">
         <v>2023</v>
       </c>
@@ -18784,7 +18787,7 @@
         <v>2.3969999999999998</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2">
         <v>2023</v>
       </c>
@@ -18823,7 +18826,7 @@
         <v>2.4319999999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2">
         <v>2023</v>
       </c>
@@ -18862,7 +18865,7 @@
         <v>2.3809999999999998</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2">
         <v>2023</v>
       </c>
@@ -18901,7 +18904,7 @@
         <v>2.2029999999999998</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2">
         <v>2023</v>
       </c>
@@ -18940,7 +18943,7 @@
         <v>2.1920000000000002</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2">
         <v>2024</v>
       </c>
@@ -18979,7 +18982,7 @@
         <v>2.274</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2">
         <v>2024</v>
       </c>
@@ -19018,7 +19021,7 @@
         <v>2.4620000000000002</v>
       </c>
     </row>
-    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2">
         <v>2024</v>
       </c>
@@ -19057,7 +19060,7 @@
         <v>2.5350000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2">
         <v>2024</v>
       </c>
@@ -19096,7 +19099,7 @@
         <v>2.7410000000000001</v>
       </c>
     </row>
-    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2">
         <v>2024</v>
       </c>
@@ -19135,7 +19138,7 @@
         <v>2.7930000000000001</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2">
         <v>2024</v>
       </c>
@@ -19174,7 +19177,7 @@
         <v>2.9889999999999999</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2">
         <v>2024</v>
       </c>
@@ -19213,7 +19216,7 @@
         <v>3.1110000000000002</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2">
         <v>2024</v>
       </c>
@@ -19252,7 +19255,7 @@
         <v>3.1850000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2">
         <v>2024</v>
       </c>
@@ -19291,7 +19294,7 @@
         <v>3.1419999999999999</v>
       </c>
     </row>
-    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2">
         <v>2024</v>
       </c>
@@ -19330,7 +19333,7 @@
         <v>3.2509999999999999</v>
       </c>
     </row>
-    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2">
         <v>2024</v>
       </c>
@@ -19369,7 +19372,7 @@
         <v>3.2970000000000002</v>
       </c>
     </row>
-    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2">
         <v>2024</v>
       </c>
@@ -19408,7 +19411,7 @@
         <v>3.2309999999999999</v>
       </c>
     </row>
-    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2">
         <v>2025</v>
       </c>
@@ -19447,7 +19450,7 @@
         <v>3.3580000000000001</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2">
         <v>2025</v>
       </c>
@@ -19486,7 +19489,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2">
         <v>2025</v>
       </c>
@@ -19525,7 +19528,7 @@
         <v>3.5249999999999999</v>
       </c>
     </row>
-    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2">
         <v>2025</v>
       </c>
@@ -19564,7 +19567,7 @@
         <v>3.496</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2">
         <v>2025</v>
       </c>
@@ -19603,7 +19606,7 @@
         <v>3.5640000000000001</v>
       </c>
     </row>
-    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2">
         <v>2025</v>
       </c>
@@ -19642,7 +19645,7 @@
         <v>3.6320000000000001</v>
       </c>
     </row>
-    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2">
         <v>2025</v>
       </c>
@@ -19681,7 +19684,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2">
         <v>2025</v>
       </c>
@@ -19720,7 +19723,7 @@
         <v>4.3029999999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2">
         <v>2025</v>
       </c>
@@ -19759,7 +19762,7 @@
         <v>4.4409999999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2">
         <v>2025</v>
       </c>
@@ -19798,7 +19801,7 @@
         <v>4.7690000000000001</v>
       </c>
     </row>
-    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2">
         <v>2025</v>
       </c>
@@ -19837,7 +19840,7 @@
         <v>4.8339999999999996</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2">
         <v>2025</v>
       </c>
@@ -19876,7 +19879,7 @@
         <v>4.6840000000000002</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2">
         <v>2026</v>
       </c>
@@ -19913,6 +19916,45 @@
       </c>
       <c r="M338" s="3">
         <v>4.6260000000000003</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A339" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B339" s="18"/>
+      <c r="C339" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D339" s="1">
+        <v>3.0790000000000002</v>
+      </c>
+      <c r="E339" s="3">
+        <v>5.6180000000000003</v>
+      </c>
+      <c r="F339" s="3">
+        <v>5.577</v>
+      </c>
+      <c r="G339" s="1">
+        <v>2.6040000000000001</v>
+      </c>
+      <c r="H339" s="3">
+        <v>5.2309999999999999</v>
+      </c>
+      <c r="I339" s="1">
+        <v>2.9769999999999999</v>
+      </c>
+      <c r="J339" s="3">
+        <v>5.52</v>
+      </c>
+      <c r="K339" s="3">
+        <v>5.4139999999999997</v>
+      </c>
+      <c r="L339" s="3">
+        <v>5.8719999999999999</v>
+      </c>
+      <c r="M339" s="3">
+        <v>4.7889999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/precios_hacienda_inac.xlsx
+++ b/data_raw/precios_hacienda_inac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GIF\Análisis sectorial\Indicadores y Precios\Precios Hacienda\SERIES DE PRECIOS SEMANALES Y MENSUALES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Usuarios\PUBLICO\PDF DE HACIENDA PARA WEB\Hacienda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8118934B-1BFB-4B1D-82E6-89B0432E28AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C846C834-514F-4AC4-8D3C-D311851DACAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HACIENDA" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Cordero Gancho" sheetId="11" r:id="rId5"/>
     <sheet name="Oveja Gancho" sheetId="12" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0" concurrentManualCount="4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="36">
   <si>
     <t>Ene</t>
   </si>
@@ -1440,7 +1440,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$340</c:f>
+              <c:f>HACIENDA!$E$341</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1815,7 +1815,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$339</c:f>
+              <c:f>HACIENDA!$A$338</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1889,12 +1889,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$339</c:f>
+              <c:f>HACIENDA!$E$338:$E$340</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>5.37</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>5.6180000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.6520000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3001,7 +3007,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$339</c:f>
+              <c:f>HACIENDA!$A$340</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3075,12 +3081,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$H$339</c:f>
+              <c:f>HACIENDA!$H$338:$H$340</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>4.9130000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>5.2309999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.2640000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4182,7 +4194,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$339</c:f>
+              <c:f>HACIENDA!$A$340</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4256,12 +4268,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$339</c:f>
+              <c:f>HACIENDA!$J$338:$J$340</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>5.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>5.52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5339,7 +5357,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$339</c:f>
+              <c:f>HACIENDA!$A$340</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5413,12 +5431,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$339</c:f>
+              <c:f>HACIENDA!$J$338:$J$340</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>5.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>5.52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6009,126 +6033,6 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>HACIENDA!$A$278</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>2021</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>HACIENDA!$C$314:$C$325</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>Ene</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Feb</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Abr</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>May</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Jun</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Jul</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Ago</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Set</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Oct</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Nov</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Dic</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>HACIENDA!$M$278:$M$289</c:f>
-              <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>2.8530000000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.964</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.1920000000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.3559999999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.6019999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.8460000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.1100000000000003</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.2069999999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.3579999999999997</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4.4829999999999997</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.3630000000000004</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.9740000000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3AB9-45CA-BDF8-16AA16B0BAAE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
@@ -6146,7 +6050,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>HACIENDA!$C$314:$C$325</c:f>
+              <c:f>HACIENDA!$C$326:$C$337</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -6257,7 +6161,7 @@
           <c:spPr>
             <a:ln>
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent5"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -6266,7 +6170,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>HACIENDA!$C$314:$C$325</c:f>
+              <c:f>HACIENDA!$C$326:$C$337</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -6386,7 +6290,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>HACIENDA!$C$314:$C$325</c:f>
+              <c:f>HACIENDA!$C$326:$C$337</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -6485,7 +6389,138 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$339</c:f>
+              <c:f>HACIENDA!$A$337</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>HACIENDA!$C$326:$C$337</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Ene</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Abr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Ago</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Set</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dic</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>HACIENDA!$M$326:$M$337</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>3.3580000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2989999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.496</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.5640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.6320000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.3029999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.4409999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.7690000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.8339999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.6840000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E553-44EE-B39A-EF14F6B9F8E7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>HACIENDA!$A$340</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6502,22 +6537,11 @@
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>HACIENDA!$C$314:$C$325</c:f>
+              <c:f>HACIENDA!$C$326:$C$337</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -6561,51 +6585,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$M$326:$M$339</c:f>
+              <c:f>HACIENDA!$M$338:$M$340</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>3.3580000000000001</c:v>
+                  <c:v>4.6260000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.2989999999999999</c:v>
+                  <c:v>4.7889999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.5249999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.496</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.5640000000000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.6320000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.9</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.3029999999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.4409999999999998</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4.7690000000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.8339999999999996</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.6840000000000002</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.6260000000000003</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.7889999999999997</c:v>
+                  <c:v>4.8490000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6613,7 +6604,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E553-44EE-B39A-EF14F6B9F8E7}"/>
+              <c16:uniqueId val="{00000000-C982-4F59-921F-3FFB5F711BDE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6652,7 +6643,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>HACIENDA!$C$314:$C$325</c15:sqref>
+                          <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -6775,10 +6766,10 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>HACIENDA!$C$314:$C$325</c15:sqref>
+                          <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -6878,6 +6869,146 @@
                 <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-3AB9-45CA-BDF8-16AA16B0BAAE}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>HACIENDA!$A$278</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>Ene</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>Feb</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Mar</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Abr</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>May</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>Jun</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>Jul</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>Ago</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>Set</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>Oct</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>Nov</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>Dic</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>HACIENDA!$M$278:$M$289</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>2.8530000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2.964</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3.1920000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3.3559999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>3.6019999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>3.8460000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4.1100000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>4.2069999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>4.3579999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>4.4829999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>4.3630000000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>3.9740000000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-3AB9-45CA-BDF8-16AA16B0BAAE}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -7092,7 +7223,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9286875" cy="6048375"/>
+    <xdr:ext cx="9305925" cy="6076950"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7342,7 +7473,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9291735" cy="6045459"/>
+    <xdr:ext cx="9301454" cy="6074617"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7589,7 +7720,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9286875" cy="6048375"/>
+    <xdr:ext cx="9305925" cy="6076950"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7839,7 +7970,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9286875" cy="6048375"/>
+    <xdr:ext cx="9305925" cy="6076950"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8089,7 +8220,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9286875" cy="6048375"/>
+    <xdr:ext cx="9305925" cy="6076950"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8656,21 +8787,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M339"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M340"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" hidden="1" customWidth="1"/>
-    <col min="3" max="5" width="11.54296875" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" customWidth="1"/>
-    <col min="7" max="9" width="11.54296875" customWidth="1"/>
-    <col min="10" max="10" width="15.453125" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" customWidth="1"/>
-    <col min="12" max="13" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" customWidth="1"/>
+    <col min="12" max="13" width="11.5703125" customWidth="1"/>
     <col min="14" max="14" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
@@ -8686,7 +8817,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
@@ -8700,44 +8831,44 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D4" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D6" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C7" s="19"/>
       <c r="D7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="19"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D8" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D9" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>22</v>
       </c>
@@ -8770,7 +8901,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="27.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="16" t="s">
         <v>35</v>
@@ -8807,7 +8938,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>1998</v>
       </c>
@@ -8830,7 +8961,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>1998</v>
       </c>
@@ -8853,7 +8984,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>1999</v>
       </c>
@@ -8878,7 +9009,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>1999</v>
       </c>
@@ -8903,7 +9034,7 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>1999</v>
       </c>
@@ -8928,7 +9059,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1999</v>
       </c>
@@ -8953,7 +9084,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>1999</v>
       </c>
@@ -8978,7 +9109,7 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>1999</v>
       </c>
@@ -9003,7 +9134,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1999</v>
       </c>
@@ -9028,7 +9159,7 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>1999</v>
       </c>
@@ -9053,7 +9184,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>1999</v>
       </c>
@@ -9078,7 +9209,7 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>1999</v>
       </c>
@@ -9103,7 +9234,7 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>1999</v>
       </c>
@@ -9128,7 +9259,7 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>1999</v>
       </c>
@@ -9153,7 +9284,7 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2000</v>
       </c>
@@ -9178,7 +9309,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -9203,7 +9334,7 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2000</v>
       </c>
@@ -9228,7 +9359,7 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2000</v>
       </c>
@@ -9253,7 +9384,7 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2000</v>
       </c>
@@ -9278,7 +9409,7 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2000</v>
       </c>
@@ -9303,7 +9434,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>2000</v>
       </c>
@@ -9328,7 +9459,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>2000</v>
       </c>
@@ -9353,7 +9484,7 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2000</v>
       </c>
@@ -9378,7 +9509,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2000</v>
       </c>
@@ -9403,7 +9534,7 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2000</v>
       </c>
@@ -9428,7 +9559,7 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>2000</v>
       </c>
@@ -9453,7 +9584,7 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>2001</v>
       </c>
@@ -9478,7 +9609,7 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>2001</v>
       </c>
@@ -9503,7 +9634,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>2001</v>
       </c>
@@ -9528,7 +9659,7 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2001</v>
       </c>
@@ -9553,7 +9684,7 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>2001</v>
       </c>
@@ -9578,7 +9709,7 @@
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2001</v>
       </c>
@@ -9603,7 +9734,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>2001</v>
       </c>
@@ -9628,7 +9759,7 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>2001</v>
       </c>
@@ -9653,7 +9784,7 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>2001</v>
       </c>
@@ -9678,7 +9809,7 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>2001</v>
       </c>
@@ -9703,7 +9834,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>2001</v>
       </c>
@@ -9728,7 +9859,7 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>2001</v>
       </c>
@@ -9753,7 +9884,7 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>2002</v>
       </c>
@@ -9778,7 +9909,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>2002</v>
       </c>
@@ -9803,7 +9934,7 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>2002</v>
       </c>
@@ -9828,7 +9959,7 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>2002</v>
       </c>
@@ -9853,7 +9984,7 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>2002</v>
       </c>
@@ -9878,7 +10009,7 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>2002</v>
       </c>
@@ -9903,7 +10034,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>2002</v>
       </c>
@@ -9928,7 +10059,7 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>2002</v>
       </c>
@@ -9953,7 +10084,7 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>2002</v>
       </c>
@@ -9978,7 +10109,7 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>2002</v>
       </c>
@@ -10003,7 +10134,7 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>2002</v>
       </c>
@@ -10028,7 +10159,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>2002</v>
       </c>
@@ -10053,7 +10184,7 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>2003</v>
       </c>
@@ -10084,7 +10215,7 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>2003</v>
       </c>
@@ -10115,7 +10246,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>2003</v>
       </c>
@@ -10146,7 +10277,7 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>2003</v>
       </c>
@@ -10177,7 +10308,7 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>2003</v>
       </c>
@@ -10208,7 +10339,7 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>2003</v>
       </c>
@@ -10239,7 +10370,7 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>2003</v>
       </c>
@@ -10270,7 +10401,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>2003</v>
       </c>
@@ -10301,7 +10432,7 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>2003</v>
       </c>
@@ -10332,7 +10463,7 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>2003</v>
       </c>
@@ -10363,7 +10494,7 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>2003</v>
       </c>
@@ -10394,7 +10525,7 @@
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>2003</v>
       </c>
@@ -10425,7 +10556,7 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>2004</v>
       </c>
@@ -10456,7 +10587,7 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>2004</v>
       </c>
@@ -10487,7 +10618,7 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>2004</v>
       </c>
@@ -10518,7 +10649,7 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>2004</v>
       </c>
@@ -10549,7 +10680,7 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>2004</v>
       </c>
@@ -10580,7 +10711,7 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>2004</v>
       </c>
@@ -10611,7 +10742,7 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>2004</v>
       </c>
@@ -10642,7 +10773,7 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>2004</v>
       </c>
@@ -10673,7 +10804,7 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>2004</v>
       </c>
@@ -10704,7 +10835,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>2004</v>
       </c>
@@ -10735,7 +10866,7 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>2004</v>
       </c>
@@ -10766,7 +10897,7 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>2004</v>
       </c>
@@ -10797,7 +10928,7 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>2005</v>
       </c>
@@ -10828,7 +10959,7 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>2005</v>
       </c>
@@ -10859,7 +10990,7 @@
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>2005</v>
       </c>
@@ -10890,7 +11021,7 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>2005</v>
       </c>
@@ -10921,7 +11052,7 @@
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>2005</v>
       </c>
@@ -10952,7 +11083,7 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>2005</v>
       </c>
@@ -10983,7 +11114,7 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>2005</v>
       </c>
@@ -11014,7 +11145,7 @@
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>2005</v>
       </c>
@@ -11045,7 +11176,7 @@
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>2005</v>
       </c>
@@ -11076,7 +11207,7 @@
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>2005</v>
       </c>
@@ -11107,7 +11238,7 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>2005</v>
       </c>
@@ -11138,7 +11269,7 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>2005</v>
       </c>
@@ -11169,7 +11300,7 @@
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>2006</v>
       </c>
@@ -11200,7 +11331,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>2006</v>
       </c>
@@ -11231,7 +11362,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>2006</v>
       </c>
@@ -11262,7 +11393,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>2006</v>
       </c>
@@ -11293,7 +11424,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>2006</v>
       </c>
@@ -11324,7 +11455,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>2006</v>
       </c>
@@ -11355,7 +11486,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>2006</v>
       </c>
@@ -11386,7 +11517,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>2006</v>
       </c>
@@ -11417,7 +11548,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>2006</v>
       </c>
@@ -11448,7 +11579,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>2006</v>
       </c>
@@ -11479,7 +11610,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>2006</v>
       </c>
@@ -11510,7 +11641,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>2006</v>
       </c>
@@ -11541,7 +11672,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>2007</v>
       </c>
@@ -11572,7 +11703,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>2007</v>
       </c>
@@ -11603,7 +11734,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>2007</v>
       </c>
@@ -11634,7 +11765,7 @@
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>2007</v>
       </c>
@@ -11665,7 +11796,7 @@
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>2007</v>
       </c>
@@ -11696,7 +11827,7 @@
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>2007</v>
       </c>
@@ -11727,7 +11858,7 @@
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>2007</v>
       </c>
@@ -11758,7 +11889,7 @@
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>2007</v>
       </c>
@@ -11789,7 +11920,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>2007</v>
       </c>
@@ -11820,7 +11951,7 @@
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>2007</v>
       </c>
@@ -11851,7 +11982,7 @@
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>2007</v>
       </c>
@@ -11882,7 +12013,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>2007</v>
       </c>
@@ -11913,7 +12044,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>2008</v>
       </c>
@@ -11944,7 +12075,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>2008</v>
       </c>
@@ -11975,7 +12106,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>2008</v>
       </c>
@@ -12006,7 +12137,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>2008</v>
       </c>
@@ -12037,7 +12168,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>2008</v>
       </c>
@@ -12068,7 +12199,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>2008</v>
       </c>
@@ -12099,7 +12230,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>2008</v>
       </c>
@@ -12130,7 +12261,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>2008</v>
       </c>
@@ -12161,7 +12292,7 @@
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>2008</v>
       </c>
@@ -12192,7 +12323,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>2008</v>
       </c>
@@ -12223,7 +12354,7 @@
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>2008</v>
       </c>
@@ -12254,7 +12385,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>2008</v>
       </c>
@@ -12285,7 +12416,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>2009</v>
       </c>
@@ -12316,7 +12447,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>2009</v>
       </c>
@@ -12347,7 +12478,7 @@
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>2009</v>
       </c>
@@ -12378,7 +12509,7 @@
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>2009</v>
       </c>
@@ -12409,7 +12540,7 @@
       <c r="L137" s="3"/>
       <c r="M137" s="3"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>2009</v>
       </c>
@@ -12440,7 +12571,7 @@
       <c r="L138" s="3"/>
       <c r="M138" s="3"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>2009</v>
       </c>
@@ -12471,7 +12602,7 @@
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>2009</v>
       </c>
@@ -12502,7 +12633,7 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>2009</v>
       </c>
@@ -12533,7 +12664,7 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>2009</v>
       </c>
@@ -12564,7 +12695,7 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>2009</v>
       </c>
@@ -12595,7 +12726,7 @@
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>2009</v>
       </c>
@@ -12626,7 +12757,7 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>2009</v>
       </c>
@@ -12657,7 +12788,7 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>2010</v>
       </c>
@@ -12688,7 +12819,7 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>2010</v>
       </c>
@@ -12719,7 +12850,7 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>2010</v>
       </c>
@@ -12750,7 +12881,7 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>2010</v>
       </c>
@@ -12781,7 +12912,7 @@
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>2010</v>
       </c>
@@ -12812,7 +12943,7 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>2010</v>
       </c>
@@ -12843,7 +12974,7 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>2010</v>
       </c>
@@ -12874,7 +13005,7 @@
       <c r="L152" s="3"/>
       <c r="M152" s="3"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>2010</v>
       </c>
@@ -12905,7 +13036,7 @@
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>2010</v>
       </c>
@@ -12936,7 +13067,7 @@
       <c r="L154" s="3"/>
       <c r="M154" s="3"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>2010</v>
       </c>
@@ -12967,7 +13098,7 @@
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>2010</v>
       </c>
@@ -12998,7 +13129,7 @@
       <c r="L156" s="3"/>
       <c r="M156" s="3"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>2010</v>
       </c>
@@ -13029,7 +13160,7 @@
       <c r="L157" s="3"/>
       <c r="M157" s="3"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>2011</v>
       </c>
@@ -13062,7 +13193,7 @@
       </c>
       <c r="M158" s="3"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>2011</v>
       </c>
@@ -13095,7 +13226,7 @@
       </c>
       <c r="M159" s="3"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>2011</v>
       </c>
@@ -13128,7 +13259,7 @@
       </c>
       <c r="M160" s="3"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>2011</v>
       </c>
@@ -13161,7 +13292,7 @@
       </c>
       <c r="M161" s="3"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>2011</v>
       </c>
@@ -13194,7 +13325,7 @@
       </c>
       <c r="M162" s="3"/>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>2011</v>
       </c>
@@ -13227,7 +13358,7 @@
       </c>
       <c r="M163" s="3"/>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>2011</v>
       </c>
@@ -13260,7 +13391,7 @@
       </c>
       <c r="M164" s="3"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>2011</v>
       </c>
@@ -13293,7 +13424,7 @@
       </c>
       <c r="M165" s="3"/>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>2011</v>
       </c>
@@ -13326,7 +13457,7 @@
       </c>
       <c r="M166" s="3"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>2011</v>
       </c>
@@ -13359,7 +13490,7 @@
       </c>
       <c r="M167" s="3"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>2011</v>
       </c>
@@ -13392,7 +13523,7 @@
       </c>
       <c r="M168" s="3"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>2011</v>
       </c>
@@ -13425,7 +13556,7 @@
       </c>
       <c r="M169" s="3"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>2012</v>
       </c>
@@ -13458,7 +13589,7 @@
       </c>
       <c r="M170" s="3"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>2012</v>
       </c>
@@ -13491,7 +13622,7 @@
       </c>
       <c r="M171" s="3"/>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>2012</v>
       </c>
@@ -13524,7 +13655,7 @@
       </c>
       <c r="M172" s="3"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>2012</v>
       </c>
@@ -13557,7 +13688,7 @@
       </c>
       <c r="M173" s="3"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>2012</v>
       </c>
@@ -13590,7 +13721,7 @@
       </c>
       <c r="M174" s="3"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>2012</v>
       </c>
@@ -13623,7 +13754,7 @@
       </c>
       <c r="M175" s="3"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>2012</v>
       </c>
@@ -13656,7 +13787,7 @@
       </c>
       <c r="M176" s="3"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>2012</v>
       </c>
@@ -13689,7 +13820,7 @@
       </c>
       <c r="M177" s="3"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>2012</v>
       </c>
@@ -13722,7 +13853,7 @@
       </c>
       <c r="M178" s="3"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>2012</v>
       </c>
@@ -13755,7 +13886,7 @@
       </c>
       <c r="M179" s="3"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>2012</v>
       </c>
@@ -13788,7 +13919,7 @@
       </c>
       <c r="M180" s="3"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>2012</v>
       </c>
@@ -13821,7 +13952,7 @@
       </c>
       <c r="M181" s="3"/>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>2013</v>
       </c>
@@ -13854,7 +13985,7 @@
       </c>
       <c r="M182" s="3"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>2013</v>
       </c>
@@ -13887,7 +14018,7 @@
       </c>
       <c r="M183" s="3"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>2013</v>
       </c>
@@ -13920,7 +14051,7 @@
       </c>
       <c r="M184" s="3"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>2013</v>
       </c>
@@ -13953,7 +14084,7 @@
       </c>
       <c r="M185" s="3"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>2013</v>
       </c>
@@ -13986,7 +14117,7 @@
       </c>
       <c r="M186" s="3"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>2013</v>
       </c>
@@ -14019,7 +14150,7 @@
       </c>
       <c r="M187" s="3"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>2013</v>
       </c>
@@ -14052,7 +14183,7 @@
       </c>
       <c r="M188" s="3"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>2013</v>
       </c>
@@ -14085,7 +14216,7 @@
       </c>
       <c r="M189" s="3"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>2013</v>
       </c>
@@ -14118,7 +14249,7 @@
       </c>
       <c r="M190" s="3"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>2013</v>
       </c>
@@ -14151,7 +14282,7 @@
       </c>
       <c r="M191" s="3"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>2013</v>
       </c>
@@ -14184,7 +14315,7 @@
       </c>
       <c r="M192" s="3"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>2013</v>
       </c>
@@ -14217,7 +14348,7 @@
       </c>
       <c r="M193" s="3"/>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>2014</v>
       </c>
@@ -14250,7 +14381,7 @@
       </c>
       <c r="M194" s="3"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>2014</v>
       </c>
@@ -14283,7 +14414,7 @@
       </c>
       <c r="M195" s="3"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>2014</v>
       </c>
@@ -14316,7 +14447,7 @@
       </c>
       <c r="M196" s="3"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>2014</v>
       </c>
@@ -14349,7 +14480,7 @@
       </c>
       <c r="M197" s="3"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>2014</v>
       </c>
@@ -14382,7 +14513,7 @@
       </c>
       <c r="M198" s="3"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>2014</v>
       </c>
@@ -14415,7 +14546,7 @@
       </c>
       <c r="M199" s="3"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>2014</v>
       </c>
@@ -14448,7 +14579,7 @@
       </c>
       <c r="M200" s="3"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>2014</v>
       </c>
@@ -14481,7 +14612,7 @@
       </c>
       <c r="M201" s="3"/>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>2014</v>
       </c>
@@ -14514,7 +14645,7 @@
       </c>
       <c r="M202" s="3"/>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>2014</v>
       </c>
@@ -14547,7 +14678,7 @@
       </c>
       <c r="M203" s="3"/>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>2014</v>
       </c>
@@ -14580,7 +14711,7 @@
       </c>
       <c r="M204" s="3"/>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>2014</v>
       </c>
@@ -14613,7 +14744,7 @@
       </c>
       <c r="M205" s="3"/>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>2015</v>
       </c>
@@ -14648,7 +14779,7 @@
       </c>
       <c r="M206" s="3"/>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>2015</v>
       </c>
@@ -14684,7 +14815,7 @@
       </c>
       <c r="M207" s="3"/>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>2015</v>
       </c>
@@ -14720,7 +14851,7 @@
       </c>
       <c r="M208" s="3"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>2015</v>
       </c>
@@ -14756,7 +14887,7 @@
       </c>
       <c r="M209" s="3"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>2015</v>
       </c>
@@ -14792,7 +14923,7 @@
       </c>
       <c r="M210" s="3"/>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>2015</v>
       </c>
@@ -14828,7 +14959,7 @@
       </c>
       <c r="M211" s="3"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>2015</v>
       </c>
@@ -14864,7 +14995,7 @@
       </c>
       <c r="M212" s="3"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>2015</v>
       </c>
@@ -14900,7 +15031,7 @@
       </c>
       <c r="M213" s="3"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>2015</v>
       </c>
@@ -14936,7 +15067,7 @@
       </c>
       <c r="M214" s="3"/>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>2015</v>
       </c>
@@ -14972,7 +15103,7 @@
       </c>
       <c r="M215" s="3"/>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>2015</v>
       </c>
@@ -15008,7 +15139,7 @@
       </c>
       <c r="M216" s="3"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>2015</v>
       </c>
@@ -15044,7 +15175,7 @@
       </c>
       <c r="M217" s="3"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>2016</v>
       </c>
@@ -15080,7 +15211,7 @@
       </c>
       <c r="M218" s="3"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>2016</v>
       </c>
@@ -15116,7 +15247,7 @@
       </c>
       <c r="M219" s="3"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>2016</v>
       </c>
@@ -15152,7 +15283,7 @@
       </c>
       <c r="M220" s="3"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>2016</v>
       </c>
@@ -15188,7 +15319,7 @@
       </c>
       <c r="M221" s="3"/>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>2016</v>
       </c>
@@ -15224,7 +15355,7 @@
       </c>
       <c r="M222" s="3"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>2016</v>
       </c>
@@ -15260,7 +15391,7 @@
       </c>
       <c r="M223" s="3"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>2016</v>
       </c>
@@ -15296,7 +15427,7 @@
       </c>
       <c r="M224" s="3"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>2016</v>
       </c>
@@ -15332,7 +15463,7 @@
       </c>
       <c r="M225" s="3"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>2016</v>
       </c>
@@ -15368,7 +15499,7 @@
       </c>
       <c r="M226" s="3"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>2016</v>
       </c>
@@ -15404,7 +15535,7 @@
       </c>
       <c r="M227" s="3"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>2016</v>
       </c>
@@ -15440,7 +15571,7 @@
       </c>
       <c r="M228" s="3"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>2016</v>
       </c>
@@ -15476,7 +15607,7 @@
       </c>
       <c r="M229" s="3"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>2017</v>
       </c>
@@ -15518,7 +15649,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>2017</v>
       </c>
@@ -15560,7 +15691,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>2017</v>
       </c>
@@ -15602,7 +15733,7 @@
         <v>2.8039999999999998</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>2017</v>
       </c>
@@ -15644,7 +15775,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>2017</v>
       </c>
@@ -15686,7 +15817,7 @@
         <v>2.8839999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>2017</v>
       </c>
@@ -15728,7 +15859,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>2017</v>
       </c>
@@ -15770,7 +15901,7 @@
         <v>3.069</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>2017</v>
       </c>
@@ -15812,7 +15943,7 @@
         <v>3.052</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>2017</v>
       </c>
@@ -15854,7 +15985,7 @@
         <v>3.1309999999999998</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>2017</v>
       </c>
@@ -15896,7 +16027,7 @@
         <v>3.157</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>2017</v>
       </c>
@@ -15938,7 +16069,7 @@
         <v>3.1669999999999998</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>2017</v>
       </c>
@@ -15980,7 +16111,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>2018</v>
       </c>
@@ -16022,7 +16153,7 @@
         <v>2.8159999999999998</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>2018</v>
       </c>
@@ -16064,7 +16195,7 @@
         <v>2.7549999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>2018</v>
       </c>
@@ -16106,7 +16237,7 @@
         <v>2.762</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>2018</v>
       </c>
@@ -16148,7 +16279,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>2018</v>
       </c>
@@ -16190,7 +16321,7 @@
         <v>2.952</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>2018</v>
       </c>
@@ -16232,7 +16363,7 @@
         <v>3.0350000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>2018</v>
       </c>
@@ -16274,7 +16405,7 @@
         <v>3.085</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>2018</v>
       </c>
@@ -16316,7 +16447,7 @@
         <v>3.1659999999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>2018</v>
       </c>
@@ -16358,7 +16489,7 @@
         <v>3.0880000000000001</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>2018</v>
       </c>
@@ -16400,7 +16531,7 @@
         <v>3.105</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>2018</v>
       </c>
@@ -16442,7 +16573,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>2018</v>
       </c>
@@ -16484,7 +16615,7 @@
         <v>2.9950229617784081</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>2019</v>
       </c>
@@ -16526,7 +16657,7 @@
         <v>2.9209999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>2019</v>
       </c>
@@ -16568,7 +16699,7 @@
         <v>2.9689999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>2019</v>
       </c>
@@ -16610,7 +16741,7 @@
         <v>2.9430000000000001</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>2019</v>
       </c>
@@ -16652,7 +16783,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>2019</v>
       </c>
@@ -16694,7 +16825,7 @@
         <v>3.121</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>2019</v>
       </c>
@@ -16736,7 +16867,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>2019</v>
       </c>
@@ -16778,7 +16909,7 @@
         <v>3.431</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>2019</v>
       </c>
@@ -16820,7 +16951,7 @@
         <v>3.4119999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>2019</v>
       </c>
@@ -16862,7 +16993,7 @@
         <v>3.613</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>2019</v>
       </c>
@@ -16904,7 +17035,7 @@
         <v>3.827</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>2019</v>
       </c>
@@ -16946,7 +17077,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>2019</v>
       </c>
@@ -16988,7 +17119,7 @@
         <v>3.9329999999999998</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>2020</v>
       </c>
@@ -17030,7 +17161,7 @@
         <v>3.6349999999999998</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>2020</v>
       </c>
@@ -17072,7 +17203,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>2020</v>
       </c>
@@ -17114,7 +17245,7 @@
         <v>3.234</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>2020</v>
       </c>
@@ -17156,7 +17287,7 @@
         <v>3.202</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>2020</v>
       </c>
@@ -17198,7 +17329,7 @@
         <v>3.0590000000000002</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>2020</v>
       </c>
@@ -17240,7 +17371,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>2020</v>
       </c>
@@ -17282,7 +17413,7 @@
         <v>3.0859999999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>2020</v>
       </c>
@@ -17324,7 +17455,7 @@
         <v>3.0609999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>2020</v>
       </c>
@@ -17366,7 +17497,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>2020</v>
       </c>
@@ -17408,7 +17539,7 @@
         <v>3.093</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>2020</v>
       </c>
@@ -17450,7 +17581,7 @@
         <v>2.9820000000000002</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>2020</v>
       </c>
@@ -17492,7 +17623,7 @@
         <v>2.8410000000000002</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>2021</v>
       </c>
@@ -17533,7 +17664,7 @@
         <v>2.8530000000000002</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>2021</v>
       </c>
@@ -17575,7 +17706,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>2021</v>
       </c>
@@ -17617,7 +17748,7 @@
         <v>3.1920000000000002</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>2021</v>
       </c>
@@ -17659,7 +17790,7 @@
         <v>3.3559999999999999</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>2021</v>
       </c>
@@ -17701,7 +17832,7 @@
         <v>3.6019999999999999</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>2021</v>
       </c>
@@ -17743,7 +17874,7 @@
         <v>3.8460000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>2021</v>
       </c>
@@ -17785,7 +17916,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>2021</v>
       </c>
@@ -17827,7 +17958,7 @@
         <v>4.2069999999999999</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>2021</v>
       </c>
@@ -17869,7 +18000,7 @@
         <v>4.3579999999999997</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>2021</v>
       </c>
@@ -17911,7 +18042,7 @@
         <v>4.4829999999999997</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>2021</v>
       </c>
@@ -17953,7 +18084,7 @@
         <v>4.3630000000000004</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>2021</v>
       </c>
@@ -17995,7 +18126,7 @@
         <v>3.9740000000000002</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>2022</v>
       </c>
@@ -18037,7 +18168,7 @@
         <v>3.6070000000000002</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>2022</v>
       </c>
@@ -18079,7 +18210,7 @@
         <v>3.6589999999999998</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>2022</v>
       </c>
@@ -18121,7 +18252,7 @@
         <v>3.964</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>2022</v>
       </c>
@@ -18163,7 +18294,7 @@
         <v>4.0640000000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>2022</v>
       </c>
@@ -18202,7 +18333,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>2022</v>
       </c>
@@ -18241,7 +18372,7 @@
         <v>4.1920000000000002</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>2022</v>
       </c>
@@ -18280,7 +18411,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>2022</v>
       </c>
@@ -18319,7 +18450,7 @@
         <v>4.2949999999999999</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>2022</v>
       </c>
@@ -18358,7 +18489,7 @@
         <v>4.0940000000000003</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>2022</v>
       </c>
@@ -18397,7 +18528,7 @@
         <v>3.1629999999999998</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>2022</v>
       </c>
@@ -18436,7 +18567,7 @@
         <v>2.6560000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>2022</v>
       </c>
@@ -18475,7 +18606,7 @@
         <v>2.536</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>2023</v>
       </c>
@@ -18514,7 +18645,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>2023</v>
       </c>
@@ -18553,7 +18684,7 @@
         <v>2.7469999999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>2023</v>
       </c>
@@ -18592,7 +18723,7 @@
         <v>2.9980000000000002</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>2023</v>
       </c>
@@ -18631,7 +18762,7 @@
         <v>3.1240000000000001</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>2023</v>
       </c>
@@ -18670,7 +18801,7 @@
         <v>2.8090000000000002</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>2023</v>
       </c>
@@ -18709,7 +18840,7 @@
         <v>2.5579999999999998</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>2023</v>
       </c>
@@ -18748,7 +18879,7 @@
         <v>2.532</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>2023</v>
       </c>
@@ -18787,7 +18918,7 @@
         <v>2.3969999999999998</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>2023</v>
       </c>
@@ -18826,7 +18957,7 @@
         <v>2.4319999999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>2023</v>
       </c>
@@ -18865,7 +18996,7 @@
         <v>2.3809999999999998</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>2023</v>
       </c>
@@ -18904,7 +19035,7 @@
         <v>2.2029999999999998</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>2023</v>
       </c>
@@ -18943,7 +19074,7 @@
         <v>2.1920000000000002</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>2024</v>
       </c>
@@ -18982,7 +19113,7 @@
         <v>2.274</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>2024</v>
       </c>
@@ -19021,7 +19152,7 @@
         <v>2.4620000000000002</v>
       </c>
     </row>
-    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>2024</v>
       </c>
@@ -19060,7 +19191,7 @@
         <v>2.5350000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>2024</v>
       </c>
@@ -19099,7 +19230,7 @@
         <v>2.7410000000000001</v>
       </c>
     </row>
-    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>2024</v>
       </c>
@@ -19138,7 +19269,7 @@
         <v>2.7930000000000001</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>2024</v>
       </c>
@@ -19177,7 +19308,7 @@
         <v>2.9889999999999999</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>2024</v>
       </c>
@@ -19216,7 +19347,7 @@
         <v>3.1110000000000002</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>2024</v>
       </c>
@@ -19255,7 +19386,7 @@
         <v>3.1850000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>2024</v>
       </c>
@@ -19294,7 +19425,7 @@
         <v>3.1419999999999999</v>
       </c>
     </row>
-    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>2024</v>
       </c>
@@ -19333,7 +19464,7 @@
         <v>3.2509999999999999</v>
       </c>
     </row>
-    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>2024</v>
       </c>
@@ -19372,7 +19503,7 @@
         <v>3.2970000000000002</v>
       </c>
     </row>
-    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>2024</v>
       </c>
@@ -19411,7 +19542,7 @@
         <v>3.2309999999999999</v>
       </c>
     </row>
-    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>2025</v>
       </c>
@@ -19450,7 +19581,7 @@
         <v>3.3580000000000001</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>2025</v>
       </c>
@@ -19489,7 +19620,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>2025</v>
       </c>
@@ -19528,7 +19659,7 @@
         <v>3.5249999999999999</v>
       </c>
     </row>
-    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>2025</v>
       </c>
@@ -19567,7 +19698,7 @@
         <v>3.496</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>2025</v>
       </c>
@@ -19606,7 +19737,7 @@
         <v>3.5640000000000001</v>
       </c>
     </row>
-    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>2025</v>
       </c>
@@ -19645,7 +19776,7 @@
         <v>3.6320000000000001</v>
       </c>
     </row>
-    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>2025</v>
       </c>
@@ -19684,7 +19815,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>2025</v>
       </c>
@@ -19723,7 +19854,7 @@
         <v>4.3029999999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>2025</v>
       </c>
@@ -19762,7 +19893,7 @@
         <v>4.4409999999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>2025</v>
       </c>
@@ -19801,7 +19932,7 @@
         <v>4.7690000000000001</v>
       </c>
     </row>
-    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>2025</v>
       </c>
@@ -19840,7 +19971,7 @@
         <v>4.8339999999999996</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>2025</v>
       </c>
@@ -19879,7 +20010,7 @@
         <v>4.6840000000000002</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>2026</v>
       </c>
@@ -19918,7 +20049,7 @@
         <v>4.6260000000000003</v>
       </c>
     </row>
-    <row r="339" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>2026</v>
       </c>
@@ -19955,6 +20086,45 @@
       </c>
       <c r="M339" s="3">
         <v>4.7889999999999997</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B340" s="18"/>
+      <c r="C340" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D340" s="1">
+        <v>3.0920000000000001</v>
+      </c>
+      <c r="E340" s="3">
+        <v>5.6520000000000001</v>
+      </c>
+      <c r="F340" s="3">
+        <v>5.6269999999999998</v>
+      </c>
+      <c r="G340" s="1">
+        <v>2.62</v>
+      </c>
+      <c r="H340" s="3">
+        <v>5.2640000000000002</v>
+      </c>
+      <c r="I340" s="1">
+        <v>3.02</v>
+      </c>
+      <c r="J340" s="3">
+        <v>5.56</v>
+      </c>
+      <c r="K340" s="3">
+        <v>5.4690000000000003</v>
+      </c>
+      <c r="L340" s="3">
+        <v>5.9580000000000002</v>
+      </c>
+      <c r="M340" s="3">
+        <v>4.8490000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/precios_hacienda_inac.xlsx
+++ b/data_raw/precios_hacienda_inac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Usuarios\PUBLICO\PDF DE HACIENDA PARA WEB\Hacienda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C846C834-514F-4AC4-8D3C-D311851DACAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06B11F5D-3DD0-4BC0-A386-739D208D5666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HACIENDA" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="36">
   <si>
     <t>Ene</t>
   </si>
@@ -1440,7 +1440,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$341</c:f>
+              <c:f>HACIENDA!$E$342</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1889,10 +1889,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$338:$E$340</c:f>
+              <c:f>HACIENDA!$E$338:$E$341</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>5.37</c:v>
                 </c:pt>
@@ -1901,6 +1901,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5.6520000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.5620000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3007,7 +3010,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$340</c:f>
+              <c:f>HACIENDA!$A$341</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3081,10 +3084,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$H$338:$H$340</c:f>
+              <c:f>HACIENDA!$H$338:$H$341</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>4.9130000000000003</c:v>
                 </c:pt>
@@ -3093,6 +3096,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5.2640000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.9969999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4194,7 +4200,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$340</c:f>
+              <c:f>HACIENDA!$A$341</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4268,10 +4274,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338:$J$340</c:f>
+              <c:f>HACIENDA!$J$338:$J$341</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>5.25</c:v>
                 </c:pt>
@@ -4280,6 +4286,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5.56</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.476</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5357,7 +5366,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$340</c:f>
+              <c:f>HACIENDA!$A$341</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5431,10 +5440,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338:$J$340</c:f>
+              <c:f>HACIENDA!$J$338:$J$341</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>5.25</c:v>
                 </c:pt>
@@ -5443,6 +5452,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5.56</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.476</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6520,7 +6532,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$340</c:f>
+              <c:f>HACIENDA!$A$341</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6585,10 +6597,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$M$338:$M$340</c:f>
+              <c:f>HACIENDA!$M$338:$M$341</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>4.6260000000000003</c:v>
                 </c:pt>
@@ -6597,6 +6609,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4.8490000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.8470000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6766,7 +6781,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -6879,7 +6894,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$A$278</c15:sqref>
@@ -6906,7 +6921,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$C$326:$C$337</c15:sqref>
@@ -6956,7 +6971,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>HACIENDA!$M$278:$M$289</c15:sqref>
@@ -7006,7 +7021,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-3AB9-45CA-BDF8-16AA16B0BAAE}"/>
                   </c:ext>
@@ -8787,7 +8802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M340"/>
+  <dimension ref="A1:M341"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -20127,6 +20142,45 @@
         <v>4.8490000000000002</v>
       </c>
     </row>
+    <row r="341" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B341" s="18"/>
+      <c r="C341" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1">
+        <v>3.0680000000000001</v>
+      </c>
+      <c r="E341" s="3">
+        <v>5.5620000000000003</v>
+      </c>
+      <c r="F341" s="3">
+        <v>5.4429999999999996</v>
+      </c>
+      <c r="G341" s="1">
+        <v>2.4969999999999999</v>
+      </c>
+      <c r="H341" s="3">
+        <v>4.9969999999999999</v>
+      </c>
+      <c r="I341" s="1">
+        <v>2.984</v>
+      </c>
+      <c r="J341" s="3">
+        <v>5.476</v>
+      </c>
+      <c r="K341" s="3">
+        <v>5.3410000000000002</v>
+      </c>
+      <c r="L341" s="3">
+        <v>5.976</v>
+      </c>
+      <c r="M341" s="3">
+        <v>4.8470000000000004</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A10:A11"/>

--- a/data_raw/precios_hacienda_inac.xlsx
+++ b/data_raw/precios_hacienda_inac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Usuarios\PUBLICO\PDF DE HACIENDA PARA WEB\Hacienda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GIF\Análisis sectorial\Indicadores y Precios\Precios Hacienda\SERIES DE PRECIOS SEMANALES Y MENSUALES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06B11F5D-3DD0-4BC0-A386-739D208D5666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A51CC4-9615-4928-8DC8-28A245E71893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-6090" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HACIENDA" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="36">
   <si>
     <t>Ene</t>
   </si>
@@ -1440,7 +1440,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$342</c:f>
+              <c:f>HACIENDA!$E$343</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1889,10 +1889,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$338:$E$341</c:f>
+              <c:f>HACIENDA!$E$338:$E$342</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>5.37</c:v>
                 </c:pt>
@@ -1904,6 +1904,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5.5620000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.6849999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3010,7 +3013,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$341</c:f>
+              <c:f>HACIENDA!$A$342</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3084,10 +3087,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$H$338:$H$341</c:f>
+              <c:f>HACIENDA!$H$338:$H$342</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>4.9130000000000003</c:v>
                 </c:pt>
@@ -3099,6 +3102,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4.9969999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.2779999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4200,7 +4206,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$341</c:f>
+              <c:f>HACIENDA!$A$342</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4274,10 +4280,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338:$J$341</c:f>
+              <c:f>HACIENDA!$J$338:$J$342</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>5.25</c:v>
                 </c:pt>
@@ -4289,6 +4295,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5.476</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.6769999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5366,7 +5375,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$341</c:f>
+              <c:f>HACIENDA!$A$342</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5440,10 +5449,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338:$J$341</c:f>
+              <c:f>HACIENDA!$J$338:$J$342</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>5.25</c:v>
                 </c:pt>
@@ -5455,6 +5464,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5.476</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.6769999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6532,7 +6544,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$341</c:f>
+              <c:f>HACIENDA!$A$342</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6597,10 +6609,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$M$338:$M$341</c:f>
+              <c:f>HACIENDA!$M$338:$M$342</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>4.6260000000000003</c:v>
                 </c:pt>
@@ -6612,6 +6624,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4.8470000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7238,7 +7253,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305925" cy="6076950"/>
+    <xdr:ext cx="9286875" cy="6048375"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7488,7 +7503,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301454" cy="6074617"/>
+    <xdr:ext cx="9291735" cy="6045459"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7735,7 +7750,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305925" cy="6076950"/>
+    <xdr:ext cx="9286875" cy="6048375"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7985,7 +8000,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305925" cy="6076950"/>
+    <xdr:ext cx="9286875" cy="6048375"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8235,7 +8250,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305925" cy="6076950"/>
+    <xdr:ext cx="9286875" cy="6048375"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8802,7 +8817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M341"/>
+  <dimension ref="A1:M342"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -20181,6 +20196,45 @@
         <v>4.8470000000000004</v>
       </c>
     </row>
+    <row r="342" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A342" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B342" s="18"/>
+      <c r="C342" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D342" s="1">
+        <v>3.1120000000000001</v>
+      </c>
+      <c r="E342" s="3">
+        <v>5.6849999999999996</v>
+      </c>
+      <c r="F342" s="3">
+        <v>5.6559999999999997</v>
+      </c>
+      <c r="G342" s="1">
+        <v>2.6480000000000001</v>
+      </c>
+      <c r="H342" s="3">
+        <v>5.2779999999999996</v>
+      </c>
+      <c r="I342" s="1">
+        <v>3.0960000000000001</v>
+      </c>
+      <c r="J342" s="3">
+        <v>5.6769999999999996</v>
+      </c>
+      <c r="K342" s="3">
+        <v>5.5540000000000003</v>
+      </c>
+      <c r="L342" s="3">
+        <v>6.0949999999999998</v>
+      </c>
+      <c r="M342" s="3">
+        <v>5.12</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A10:A11"/>

--- a/data_raw/precios_hacienda_inac.xlsx
+++ b/data_raw/precios_hacienda_inac.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GIF\Análisis sectorial\Indicadores y Precios\Precios Hacienda\SERIES DE PRECIOS SEMANALES Y MENSUALES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A51CC4-9615-4928-8DC8-28A245E71893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830CB6EF-DBCE-494E-82B7-80AC6DFFB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-6090" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HACIENDA" sheetId="1" r:id="rId1"/>
@@ -3104,7 +3104,7 @@
                   <c:v>4.9969999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.2779999999999996</c:v>
+                  <c:v>5.2729999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4297,7 +4297,7 @@
                   <c:v>5.476</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.6769999999999996</c:v>
+                  <c:v>5.6749999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5466,7 +5466,7 @@
                   <c:v>5.476</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.6769999999999996</c:v>
+                  <c:v>5.6749999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7253,7 +7253,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9286875" cy="6048375"/>
+    <xdr:ext cx="9283700" cy="6045200"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7503,7 +7503,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9291735" cy="6045459"/>
+    <xdr:ext cx="9278776" cy="6045459"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7750,7 +7750,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9286875" cy="6048375"/>
+    <xdr:ext cx="9283700" cy="6045200"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8000,7 +8000,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9286875" cy="6048375"/>
+    <xdr:ext cx="9283700" cy="6045200"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8250,7 +8250,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9286875" cy="6048375"/>
+    <xdr:ext cx="9283700" cy="6045200"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8818,20 +8818,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M342"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" hidden="1" customWidth="1"/>
-    <col min="3" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" customWidth="1"/>
-    <col min="12" max="13" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" hidden="1" customWidth="1"/>
+    <col min="3" max="5" width="11.54296875" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" customWidth="1"/>
+    <col min="7" max="9" width="11.54296875" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" customWidth="1"/>
+    <col min="12" max="13" width="11.54296875" customWidth="1"/>
     <col min="14" max="14" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
       <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
@@ -8861,44 +8861,44 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D4" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D6" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C7" s="19"/>
       <c r="D7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="19"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D8" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D9" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
         <v>22</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="27.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="27.5" x14ac:dyDescent="0.35">
       <c r="A11" s="20"/>
       <c r="B11" s="16" t="s">
         <v>35</v>
@@ -8968,7 +8968,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>1998</v>
       </c>
@@ -8991,7 +8991,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>1998</v>
       </c>
@@ -9014,7 +9014,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>1999</v>
       </c>
@@ -9039,7 +9039,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>1999</v>
       </c>
@@ -9064,7 +9064,7 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>1999</v>
       </c>
@@ -9089,7 +9089,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>1999</v>
       </c>
@@ -9114,7 +9114,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>1999</v>
       </c>
@@ -9139,7 +9139,7 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>1999</v>
       </c>
@@ -9164,7 +9164,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>1999</v>
       </c>
@@ -9189,7 +9189,7 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>1999</v>
       </c>
@@ -9214,7 +9214,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>1999</v>
       </c>
@@ -9239,7 +9239,7 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>1999</v>
       </c>
@@ -9264,7 +9264,7 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>1999</v>
       </c>
@@ -9289,7 +9289,7 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>1999</v>
       </c>
@@ -9314,7 +9314,7 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2000</v>
       </c>
@@ -9339,7 +9339,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -9364,7 +9364,7 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2000</v>
       </c>
@@ -9389,7 +9389,7 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2000</v>
       </c>
@@ -9414,7 +9414,7 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2000</v>
       </c>
@@ -9439,7 +9439,7 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2000</v>
       </c>
@@ -9464,7 +9464,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2000</v>
       </c>
@@ -9489,7 +9489,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2000</v>
       </c>
@@ -9514,7 +9514,7 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2000</v>
       </c>
@@ -9539,7 +9539,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2000</v>
       </c>
@@ -9564,7 +9564,7 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2000</v>
       </c>
@@ -9589,7 +9589,7 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2000</v>
       </c>
@@ -9614,7 +9614,7 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2001</v>
       </c>
@@ -9639,7 +9639,7 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2001</v>
       </c>
@@ -9664,7 +9664,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2001</v>
       </c>
@@ -9689,7 +9689,7 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2001</v>
       </c>
@@ -9714,7 +9714,7 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>2001</v>
       </c>
@@ -9739,7 +9739,7 @@
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>2001</v>
       </c>
@@ -9764,7 +9764,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>2001</v>
       </c>
@@ -9789,7 +9789,7 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>2001</v>
       </c>
@@ -9814,7 +9814,7 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>2001</v>
       </c>
@@ -9839,7 +9839,7 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>2001</v>
       </c>
@@ -9864,7 +9864,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>2001</v>
       </c>
@@ -9889,7 +9889,7 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>2001</v>
       </c>
@@ -9914,7 +9914,7 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>2002</v>
       </c>
@@ -9939,7 +9939,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>2002</v>
       </c>
@@ -9964,7 +9964,7 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>2002</v>
       </c>
@@ -9989,7 +9989,7 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>2002</v>
       </c>
@@ -10014,7 +10014,7 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>2002</v>
       </c>
@@ -10039,7 +10039,7 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2002</v>
       </c>
@@ -10064,7 +10064,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2002</v>
       </c>
@@ -10089,7 +10089,7 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2002</v>
       </c>
@@ -10114,7 +10114,7 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2002</v>
       </c>
@@ -10139,7 +10139,7 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2002</v>
       </c>
@@ -10164,7 +10164,7 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2002</v>
       </c>
@@ -10189,7 +10189,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2002</v>
       </c>
@@ -10214,7 +10214,7 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2003</v>
       </c>
@@ -10245,7 +10245,7 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2003</v>
       </c>
@@ -10276,7 +10276,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2003</v>
       </c>
@@ -10307,7 +10307,7 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2003</v>
       </c>
@@ -10338,7 +10338,7 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2003</v>
       </c>
@@ -10369,7 +10369,7 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2003</v>
       </c>
@@ -10400,7 +10400,7 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2003</v>
       </c>
@@ -10431,7 +10431,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2003</v>
       </c>
@@ -10462,7 +10462,7 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>2003</v>
       </c>
@@ -10493,7 +10493,7 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2003</v>
       </c>
@@ -10524,7 +10524,7 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2003</v>
       </c>
@@ -10555,7 +10555,7 @@
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>2003</v>
       </c>
@@ -10586,7 +10586,7 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>2004</v>
       </c>
@@ -10617,7 +10617,7 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2004</v>
       </c>
@@ -10648,7 +10648,7 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>2004</v>
       </c>
@@ -10679,7 +10679,7 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2004</v>
       </c>
@@ -10710,7 +10710,7 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2004</v>
       </c>
@@ -10741,7 +10741,7 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2004</v>
       </c>
@@ -10772,7 +10772,7 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2004</v>
       </c>
@@ -10803,7 +10803,7 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2004</v>
       </c>
@@ -10834,7 +10834,7 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2004</v>
       </c>
@@ -10865,7 +10865,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>2004</v>
       </c>
@@ -10896,7 +10896,7 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2004</v>
       </c>
@@ -10927,7 +10927,7 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2004</v>
       </c>
@@ -10958,7 +10958,7 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2005</v>
       </c>
@@ -10989,7 +10989,7 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2005</v>
       </c>
@@ -11020,7 +11020,7 @@
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2005</v>
       </c>
@@ -11051,7 +11051,7 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>2005</v>
       </c>
@@ -11082,7 +11082,7 @@
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2005</v>
       </c>
@@ -11113,7 +11113,7 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2005</v>
       </c>
@@ -11144,7 +11144,7 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>2005</v>
       </c>
@@ -11175,7 +11175,7 @@
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>2005</v>
       </c>
@@ -11206,7 +11206,7 @@
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>2005</v>
       </c>
@@ -11237,7 +11237,7 @@
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2005</v>
       </c>
@@ -11268,7 +11268,7 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2005</v>
       </c>
@@ -11299,7 +11299,7 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>2005</v>
       </c>
@@ -11330,7 +11330,7 @@
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2006</v>
       </c>
@@ -11361,7 +11361,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2006</v>
       </c>
@@ -11392,7 +11392,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2006</v>
       </c>
@@ -11423,7 +11423,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2006</v>
       </c>
@@ -11454,7 +11454,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2006</v>
       </c>
@@ -11485,7 +11485,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2006</v>
       </c>
@@ -11516,7 +11516,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>2006</v>
       </c>
@@ -11547,7 +11547,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2006</v>
       </c>
@@ -11578,7 +11578,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>2006</v>
       </c>
@@ -11609,7 +11609,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>2006</v>
       </c>
@@ -11640,7 +11640,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2006</v>
       </c>
@@ -11671,7 +11671,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>2006</v>
       </c>
@@ -11702,7 +11702,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>2007</v>
       </c>
@@ -11733,7 +11733,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2007</v>
       </c>
@@ -11764,7 +11764,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>2007</v>
       </c>
@@ -11795,7 +11795,7 @@
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2007</v>
       </c>
@@ -11826,7 +11826,7 @@
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2007</v>
       </c>
@@ -11857,7 +11857,7 @@
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>2007</v>
       </c>
@@ -11888,7 +11888,7 @@
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2007</v>
       </c>
@@ -11919,7 +11919,7 @@
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>2007</v>
       </c>
@@ -11950,7 +11950,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>2007</v>
       </c>
@@ -11981,7 +11981,7 @@
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>2007</v>
       </c>
@@ -12012,7 +12012,7 @@
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>2007</v>
       </c>
@@ -12043,7 +12043,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>2007</v>
       </c>
@@ -12074,7 +12074,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>2008</v>
       </c>
@@ -12105,7 +12105,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>2008</v>
       </c>
@@ -12136,7 +12136,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>2008</v>
       </c>
@@ -12167,7 +12167,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>2008</v>
       </c>
@@ -12198,7 +12198,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>2008</v>
       </c>
@@ -12229,7 +12229,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>2008</v>
       </c>
@@ -12260,7 +12260,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>2008</v>
       </c>
@@ -12291,7 +12291,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>2008</v>
       </c>
@@ -12322,7 +12322,7 @@
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>2008</v>
       </c>
@@ -12353,7 +12353,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>2008</v>
       </c>
@@ -12384,7 +12384,7 @@
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>2008</v>
       </c>
@@ -12415,7 +12415,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>2008</v>
       </c>
@@ -12446,7 +12446,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>2009</v>
       </c>
@@ -12477,7 +12477,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>2009</v>
       </c>
@@ -12508,7 +12508,7 @@
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>2009</v>
       </c>
@@ -12539,7 +12539,7 @@
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>2009</v>
       </c>
@@ -12570,7 +12570,7 @@
       <c r="L137" s="3"/>
       <c r="M137" s="3"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>2009</v>
       </c>
@@ -12601,7 +12601,7 @@
       <c r="L138" s="3"/>
       <c r="M138" s="3"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>2009</v>
       </c>
@@ -12632,7 +12632,7 @@
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>2009</v>
       </c>
@@ -12663,7 +12663,7 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>2009</v>
       </c>
@@ -12694,7 +12694,7 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>2009</v>
       </c>
@@ -12725,7 +12725,7 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>2009</v>
       </c>
@@ -12756,7 +12756,7 @@
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>2009</v>
       </c>
@@ -12787,7 +12787,7 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>2009</v>
       </c>
@@ -12818,7 +12818,7 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>2010</v>
       </c>
@@ -12849,7 +12849,7 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>2010</v>
       </c>
@@ -12880,7 +12880,7 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>2010</v>
       </c>
@@ -12911,7 +12911,7 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>2010</v>
       </c>
@@ -12942,7 +12942,7 @@
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>2010</v>
       </c>
@@ -12973,7 +12973,7 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>2010</v>
       </c>
@@ -13004,7 +13004,7 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>2010</v>
       </c>
@@ -13035,7 +13035,7 @@
       <c r="L152" s="3"/>
       <c r="M152" s="3"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>2010</v>
       </c>
@@ -13066,7 +13066,7 @@
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>2010</v>
       </c>
@@ -13097,7 +13097,7 @@
       <c r="L154" s="3"/>
       <c r="M154" s="3"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>2010</v>
       </c>
@@ -13128,7 +13128,7 @@
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>2010</v>
       </c>
@@ -13159,7 +13159,7 @@
       <c r="L156" s="3"/>
       <c r="M156" s="3"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>2010</v>
       </c>
@@ -13190,7 +13190,7 @@
       <c r="L157" s="3"/>
       <c r="M157" s="3"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>2011</v>
       </c>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="M158" s="3"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>2011</v>
       </c>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="M159" s="3"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>2011</v>
       </c>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="M160" s="3"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>2011</v>
       </c>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="M161" s="3"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>2011</v>
       </c>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="M162" s="3"/>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>2011</v>
       </c>
@@ -13388,7 +13388,7 @@
       </c>
       <c r="M163" s="3"/>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>2011</v>
       </c>
@@ -13421,7 +13421,7 @@
       </c>
       <c r="M164" s="3"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>2011</v>
       </c>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M165" s="3"/>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>2011</v>
       </c>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="M166" s="3"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>2011</v>
       </c>
@@ -13520,7 +13520,7 @@
       </c>
       <c r="M167" s="3"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>2011</v>
       </c>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="M168" s="3"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>2011</v>
       </c>
@@ -13586,7 +13586,7 @@
       </c>
       <c r="M169" s="3"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>2012</v>
       </c>
@@ -13619,7 +13619,7 @@
       </c>
       <c r="M170" s="3"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>2012</v>
       </c>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="M171" s="3"/>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>2012</v>
       </c>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="M172" s="3"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>2012</v>
       </c>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="M173" s="3"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>2012</v>
       </c>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="M174" s="3"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>2012</v>
       </c>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="M175" s="3"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>2012</v>
       </c>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="M176" s="3"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>2012</v>
       </c>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="M177" s="3"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>2012</v>
       </c>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="M178" s="3"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>2012</v>
       </c>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="M179" s="3"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>2012</v>
       </c>
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M180" s="3"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>2012</v>
       </c>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="M181" s="3"/>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>2013</v>
       </c>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="M182" s="3"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>2013</v>
       </c>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="M183" s="3"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>2013</v>
       </c>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="M184" s="3"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>2013</v>
       </c>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="M185" s="3"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>2013</v>
       </c>
@@ -14147,7 +14147,7 @@
       </c>
       <c r="M186" s="3"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>2013</v>
       </c>
@@ -14180,7 +14180,7 @@
       </c>
       <c r="M187" s="3"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>2013</v>
       </c>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="M188" s="3"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>2013</v>
       </c>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="M189" s="3"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>2013</v>
       </c>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="M190" s="3"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>2013</v>
       </c>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="M191" s="3"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>2013</v>
       </c>
@@ -14345,7 +14345,7 @@
       </c>
       <c r="M192" s="3"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>2013</v>
       </c>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="M193" s="3"/>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>2014</v>
       </c>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="M194" s="3"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>2014</v>
       </c>
@@ -14444,7 +14444,7 @@
       </c>
       <c r="M195" s="3"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>2014</v>
       </c>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="M196" s="3"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>2014</v>
       </c>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="M197" s="3"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>2014</v>
       </c>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="M198" s="3"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>2014</v>
       </c>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="M199" s="3"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>2014</v>
       </c>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="M200" s="3"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>2014</v>
       </c>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="M201" s="3"/>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>2014</v>
       </c>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M202" s="3"/>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>2014</v>
       </c>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="M203" s="3"/>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>2014</v>
       </c>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="M204" s="3"/>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>2014</v>
       </c>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M205" s="3"/>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>2015</v>
       </c>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M206" s="3"/>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>2015</v>
       </c>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="M207" s="3"/>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>2015</v>
       </c>
@@ -14881,7 +14881,7 @@
       </c>
       <c r="M208" s="3"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>2015</v>
       </c>
@@ -14917,7 +14917,7 @@
       </c>
       <c r="M209" s="3"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>2015</v>
       </c>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="M210" s="3"/>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>2015</v>
       </c>
@@ -14989,7 +14989,7 @@
       </c>
       <c r="M211" s="3"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>2015</v>
       </c>
@@ -15025,7 +15025,7 @@
       </c>
       <c r="M212" s="3"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>2015</v>
       </c>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="M213" s="3"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>2015</v>
       </c>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="M214" s="3"/>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>2015</v>
       </c>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="M215" s="3"/>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>2015</v>
       </c>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="M216" s="3"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>2015</v>
       </c>
@@ -15205,7 +15205,7 @@
       </c>
       <c r="M217" s="3"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>2016</v>
       </c>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="M218" s="3"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>2016</v>
       </c>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="M219" s="3"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>2016</v>
       </c>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="M220" s="3"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>2016</v>
       </c>
@@ -15349,7 +15349,7 @@
       </c>
       <c r="M221" s="3"/>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>2016</v>
       </c>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="M222" s="3"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>2016</v>
       </c>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="M223" s="3"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>2016</v>
       </c>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="M224" s="3"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>2016</v>
       </c>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="M225" s="3"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>2016</v>
       </c>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="M226" s="3"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>2016</v>
       </c>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="M227" s="3"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>2016</v>
       </c>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="M228" s="3"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>2016</v>
       </c>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="M229" s="3"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>2017</v>
       </c>
@@ -15679,7 +15679,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>2017</v>
       </c>
@@ -15721,7 +15721,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>2017</v>
       </c>
@@ -15763,7 +15763,7 @@
         <v>2.8039999999999998</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>2017</v>
       </c>
@@ -15805,7 +15805,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>2017</v>
       </c>
@@ -15847,7 +15847,7 @@
         <v>2.8839999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>2017</v>
       </c>
@@ -15889,7 +15889,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>2017</v>
       </c>
@@ -15931,7 +15931,7 @@
         <v>3.069</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>2017</v>
       </c>
@@ -15973,7 +15973,7 @@
         <v>3.052</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>2017</v>
       </c>
@@ -16015,7 +16015,7 @@
         <v>3.1309999999999998</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>2017</v>
       </c>
@@ -16057,7 +16057,7 @@
         <v>3.157</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>2017</v>
       </c>
@@ -16099,7 +16099,7 @@
         <v>3.1669999999999998</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>2017</v>
       </c>
@@ -16141,7 +16141,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>2018</v>
       </c>
@@ -16183,7 +16183,7 @@
         <v>2.8159999999999998</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>2018</v>
       </c>
@@ -16225,7 +16225,7 @@
         <v>2.7549999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>2018</v>
       </c>
@@ -16267,7 +16267,7 @@
         <v>2.762</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A245" s="2">
         <v>2018</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A246" s="2">
         <v>2018</v>
       </c>
@@ -16351,7 +16351,7 @@
         <v>2.952</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A247" s="2">
         <v>2018</v>
       </c>
@@ -16393,7 +16393,7 @@
         <v>3.0350000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A248" s="2">
         <v>2018</v>
       </c>
@@ -16435,7 +16435,7 @@
         <v>3.085</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A249" s="2">
         <v>2018</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>3.1659999999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A250" s="2">
         <v>2018</v>
       </c>
@@ -16519,7 +16519,7 @@
         <v>3.0880000000000001</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A251" s="2">
         <v>2018</v>
       </c>
@@ -16561,7 +16561,7 @@
         <v>3.105</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A252" s="2">
         <v>2018</v>
       </c>
@@ -16603,7 +16603,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A253" s="2">
         <v>2018</v>
       </c>
@@ -16645,7 +16645,7 @@
         <v>2.9950229617784081</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A254" s="2">
         <v>2019</v>
       </c>
@@ -16687,7 +16687,7 @@
         <v>2.9209999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A255" s="2">
         <v>2019</v>
       </c>
@@ -16729,7 +16729,7 @@
         <v>2.9689999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A256" s="2">
         <v>2019</v>
       </c>
@@ -16771,7 +16771,7 @@
         <v>2.9430000000000001</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A257" s="2">
         <v>2019</v>
       </c>
@@ -16813,7 +16813,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A258" s="2">
         <v>2019</v>
       </c>
@@ -16855,7 +16855,7 @@
         <v>3.121</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A259" s="2">
         <v>2019</v>
       </c>
@@ -16897,7 +16897,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A260" s="2">
         <v>2019</v>
       </c>
@@ -16939,7 +16939,7 @@
         <v>3.431</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A261" s="2">
         <v>2019</v>
       </c>
@@ -16981,7 +16981,7 @@
         <v>3.4119999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2">
         <v>2019</v>
       </c>
@@ -17023,7 +17023,7 @@
         <v>3.613</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A263" s="2">
         <v>2019</v>
       </c>
@@ -17065,7 +17065,7 @@
         <v>3.827</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A264" s="2">
         <v>2019</v>
       </c>
@@ -17107,7 +17107,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A265" s="2">
         <v>2019</v>
       </c>
@@ -17149,7 +17149,7 @@
         <v>3.9329999999999998</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A266" s="2">
         <v>2020</v>
       </c>
@@ -17191,7 +17191,7 @@
         <v>3.6349999999999998</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A267" s="2">
         <v>2020</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A268" s="2">
         <v>2020</v>
       </c>
@@ -17275,7 +17275,7 @@
         <v>3.234</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A269" s="2">
         <v>2020</v>
       </c>
@@ -17317,7 +17317,7 @@
         <v>3.202</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A270" s="2">
         <v>2020</v>
       </c>
@@ -17359,7 +17359,7 @@
         <v>3.0590000000000002</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A271" s="2">
         <v>2020</v>
       </c>
@@ -17401,7 +17401,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A272" s="2">
         <v>2020</v>
       </c>
@@ -17443,7 +17443,7 @@
         <v>3.0859999999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A273" s="2">
         <v>2020</v>
       </c>
@@ -17485,7 +17485,7 @@
         <v>3.0609999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A274" s="2">
         <v>2020</v>
       </c>
@@ -17527,7 +17527,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A275" s="2">
         <v>2020</v>
       </c>
@@ -17569,7 +17569,7 @@
         <v>3.093</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A276" s="2">
         <v>2020</v>
       </c>
@@ -17611,7 +17611,7 @@
         <v>2.9820000000000002</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2">
         <v>2020</v>
       </c>
@@ -17653,7 +17653,7 @@
         <v>2.8410000000000002</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2">
         <v>2021</v>
       </c>
@@ -17694,7 +17694,7 @@
         <v>2.8530000000000002</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2">
         <v>2021</v>
       </c>
@@ -17736,7 +17736,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2">
         <v>2021</v>
       </c>
@@ -17778,7 +17778,7 @@
         <v>3.1920000000000002</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2">
         <v>2021</v>
       </c>
@@ -17820,7 +17820,7 @@
         <v>3.3559999999999999</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2">
         <v>2021</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>3.6019999999999999</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2">
         <v>2021</v>
       </c>
@@ -17904,7 +17904,7 @@
         <v>3.8460000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2">
         <v>2021</v>
       </c>
@@ -17946,7 +17946,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2">
         <v>2021</v>
       </c>
@@ -17988,7 +17988,7 @@
         <v>4.2069999999999999</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2">
         <v>2021</v>
       </c>
@@ -18030,7 +18030,7 @@
         <v>4.3579999999999997</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2">
         <v>2021</v>
       </c>
@@ -18072,7 +18072,7 @@
         <v>4.4829999999999997</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2">
         <v>2021</v>
       </c>
@@ -18114,7 +18114,7 @@
         <v>4.3630000000000004</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2">
         <v>2021</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>3.9740000000000002</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2">
         <v>2022</v>
       </c>
@@ -18198,7 +18198,7 @@
         <v>3.6070000000000002</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2">
         <v>2022</v>
       </c>
@@ -18240,7 +18240,7 @@
         <v>3.6589999999999998</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2">
         <v>2022</v>
       </c>
@@ -18282,7 +18282,7 @@
         <v>3.964</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2">
         <v>2022</v>
       </c>
@@ -18324,7 +18324,7 @@
         <v>4.0640000000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2">
         <v>2022</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2">
         <v>2022</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>4.1920000000000002</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2">
         <v>2022</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2">
         <v>2022</v>
       </c>
@@ -18480,7 +18480,7 @@
         <v>4.2949999999999999</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2">
         <v>2022</v>
       </c>
@@ -18519,7 +18519,7 @@
         <v>4.0940000000000003</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2">
         <v>2022</v>
       </c>
@@ -18558,7 +18558,7 @@
         <v>3.1629999999999998</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2">
         <v>2022</v>
       </c>
@@ -18597,7 +18597,7 @@
         <v>2.6560000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2">
         <v>2022</v>
       </c>
@@ -18636,7 +18636,7 @@
         <v>2.536</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2">
         <v>2023</v>
       </c>
@@ -18675,7 +18675,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2">
         <v>2023</v>
       </c>
@@ -18714,7 +18714,7 @@
         <v>2.7469999999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2">
         <v>2023</v>
       </c>
@@ -18753,7 +18753,7 @@
         <v>2.9980000000000002</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2">
         <v>2023</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>3.1240000000000001</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2">
         <v>2023</v>
       </c>
@@ -18831,7 +18831,7 @@
         <v>2.8090000000000002</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2">
         <v>2023</v>
       </c>
@@ -18870,7 +18870,7 @@
         <v>2.5579999999999998</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2">
         <v>2023</v>
       </c>
@@ -18909,7 +18909,7 @@
         <v>2.532</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2">
         <v>2023</v>
       </c>
@@ -18948,7 +18948,7 @@
         <v>2.3969999999999998</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2">
         <v>2023</v>
       </c>
@@ -18987,7 +18987,7 @@
         <v>2.4319999999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2">
         <v>2023</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>2.3809999999999998</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2">
         <v>2023</v>
       </c>
@@ -19065,7 +19065,7 @@
         <v>2.2029999999999998</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2">
         <v>2023</v>
       </c>
@@ -19104,7 +19104,7 @@
         <v>2.1920000000000002</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2">
         <v>2024</v>
       </c>
@@ -19143,7 +19143,7 @@
         <v>2.274</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2">
         <v>2024</v>
       </c>
@@ -19182,7 +19182,7 @@
         <v>2.4620000000000002</v>
       </c>
     </row>
-    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2">
         <v>2024</v>
       </c>
@@ -19221,7 +19221,7 @@
         <v>2.5350000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2">
         <v>2024</v>
       </c>
@@ -19260,7 +19260,7 @@
         <v>2.7410000000000001</v>
       </c>
     </row>
-    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2">
         <v>2024</v>
       </c>
@@ -19299,7 +19299,7 @@
         <v>2.7930000000000001</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2">
         <v>2024</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>2.9889999999999999</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2">
         <v>2024</v>
       </c>
@@ -19377,7 +19377,7 @@
         <v>3.1110000000000002</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2">
         <v>2024</v>
       </c>
@@ -19416,7 +19416,7 @@
         <v>3.1850000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2">
         <v>2024</v>
       </c>
@@ -19455,7 +19455,7 @@
         <v>3.1419999999999999</v>
       </c>
     </row>
-    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2">
         <v>2024</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>3.2509999999999999</v>
       </c>
     </row>
-    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2">
         <v>2024</v>
       </c>
@@ -19533,7 +19533,7 @@
         <v>3.2970000000000002</v>
       </c>
     </row>
-    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2">
         <v>2024</v>
       </c>
@@ -19572,7 +19572,7 @@
         <v>3.2309999999999999</v>
       </c>
     </row>
-    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2">
         <v>2025</v>
       </c>
@@ -19611,7 +19611,7 @@
         <v>3.3580000000000001</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2">
         <v>2025</v>
       </c>
@@ -19650,7 +19650,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2">
         <v>2025</v>
       </c>
@@ -19689,7 +19689,7 @@
         <v>3.5249999999999999</v>
       </c>
     </row>
-    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2">
         <v>2025</v>
       </c>
@@ -19728,7 +19728,7 @@
         <v>3.496</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2">
         <v>2025</v>
       </c>
@@ -19767,7 +19767,7 @@
         <v>3.5640000000000001</v>
       </c>
     </row>
-    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2">
         <v>2025</v>
       </c>
@@ -19806,7 +19806,7 @@
         <v>3.6320000000000001</v>
       </c>
     </row>
-    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2">
         <v>2025</v>
       </c>
@@ -19845,7 +19845,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2">
         <v>2025</v>
       </c>
@@ -19884,7 +19884,7 @@
         <v>4.3029999999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2">
         <v>2025</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>4.4409999999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2">
         <v>2025</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>4.7690000000000001</v>
       </c>
     </row>
-    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2">
         <v>2025</v>
       </c>
@@ -20001,7 +20001,7 @@
         <v>4.8339999999999996</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2">
         <v>2025</v>
       </c>
@@ -20040,7 +20040,7 @@
         <v>4.6840000000000002</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2">
         <v>2026</v>
       </c>
@@ -20079,7 +20079,7 @@
         <v>4.6260000000000003</v>
       </c>
     </row>
-    <row r="339" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2">
         <v>2026</v>
       </c>
@@ -20118,7 +20118,7 @@
         <v>4.7889999999999997</v>
       </c>
     </row>
-    <row r="340" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2">
         <v>2026</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>4.8490000000000002</v>
       </c>
     </row>
-    <row r="341" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2">
         <v>2026</v>
       </c>
@@ -20196,7 +20196,7 @@
         <v>4.8470000000000004</v>
       </c>
     </row>
-    <row r="342" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2">
         <v>2026</v>
       </c>
@@ -20214,19 +20214,19 @@
         <v>5.6559999999999997</v>
       </c>
       <c r="G342" s="1">
-        <v>2.6480000000000001</v>
+        <v>2.6440000000000001</v>
       </c>
       <c r="H342" s="3">
-        <v>5.2779999999999996</v>
+        <v>5.2729999999999997</v>
       </c>
       <c r="I342" s="1">
-        <v>3.0960000000000001</v>
+        <v>3.0939999999999999</v>
       </c>
       <c r="J342" s="3">
-        <v>5.6769999999999996</v>
+        <v>5.6749999999999998</v>
       </c>
       <c r="K342" s="3">
-        <v>5.5540000000000003</v>
+        <v>5.55</v>
       </c>
       <c r="L342" s="3">
         <v>6.0949999999999998</v>

--- a/data_raw/precios_hacienda_inac.xlsx
+++ b/data_raw/precios_hacienda_inac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GIF\Análisis sectorial\Indicadores y Precios\Precios Hacienda\SERIES DE PRECIOS SEMANALES Y MENSUALES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830CB6EF-DBCE-494E-82B7-80AC6DFFB43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6228876A-811C-4C5B-90F6-5567191AA717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HACIENDA" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="36">
   <si>
     <t>Ene</t>
   </si>
@@ -1440,7 +1440,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$343</c:f>
+              <c:f>HACIENDA!$E$344</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1889,10 +1889,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$338:$E$342</c:f>
+              <c:f>HACIENDA!$E$338:$E$343</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>5.37</c:v>
                 </c:pt>
@@ -1907,6 +1907,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5.6849999999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.7450000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3013,7 +3016,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$342</c:f>
+              <c:f>HACIENDA!$A$343</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3087,10 +3090,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$H$338:$H$342</c:f>
+              <c:f>HACIENDA!$H$338:$H$343</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>4.9130000000000003</c:v>
                 </c:pt>
@@ -3105,6 +3108,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5.2729999999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.3079999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4206,7 +4212,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$342</c:f>
+              <c:f>HACIENDA!$A$343</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4280,10 +4286,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338:$J$342</c:f>
+              <c:f>HACIENDA!$J$338:$J$343</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>5.25</c:v>
                 </c:pt>
@@ -4298,6 +4304,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5.6749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.6779999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5375,7 +5384,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$342</c:f>
+              <c:f>HACIENDA!$A$343</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5449,10 +5458,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338:$J$342</c:f>
+              <c:f>HACIENDA!$J$338:$J$343</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>5.25</c:v>
                 </c:pt>
@@ -5467,6 +5476,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5.6749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.6779999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6544,7 +6556,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$342</c:f>
+              <c:f>HACIENDA!$A$343</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6609,10 +6621,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$M$338:$M$342</c:f>
+              <c:f>HACIENDA!$M$338:$M$343</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>4.6260000000000003</c:v>
                 </c:pt>
@@ -6627,6 +6639,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5.12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.0919999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7253,7 +7268,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9283700" cy="6045200"/>
+    <xdr:ext cx="9286875" cy="6048375"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7503,7 +7518,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9278776" cy="6045459"/>
+    <xdr:ext cx="9291735" cy="6045459"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -7750,7 +7765,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9283700" cy="6045200"/>
+    <xdr:ext cx="9286875" cy="6048375"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8000,7 +8015,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9283700" cy="6045200"/>
+    <xdr:ext cx="9286875" cy="6048375"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8250,7 +8265,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9283700" cy="6045200"/>
+    <xdr:ext cx="9286875" cy="6048375"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8817,21 +8832,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M342"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M343"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" hidden="1" customWidth="1"/>
-    <col min="3" max="5" width="11.54296875" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" customWidth="1"/>
-    <col min="7" max="9" width="11.54296875" customWidth="1"/>
-    <col min="10" max="10" width="15.453125" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" customWidth="1"/>
-    <col min="12" max="13" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" customWidth="1"/>
+    <col min="12" max="13" width="11.5703125" customWidth="1"/>
     <col min="14" max="14" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
@@ -8847,7 +8862,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
@@ -8861,44 +8876,44 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D4" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D6" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C7" s="19"/>
       <c r="D7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="19"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D8" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D9" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>22</v>
       </c>
@@ -8931,7 +8946,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="27.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="16" t="s">
         <v>35</v>
@@ -8968,7 +8983,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>1998</v>
       </c>
@@ -8991,7 +9006,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>1998</v>
       </c>
@@ -9014,7 +9029,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>1999</v>
       </c>
@@ -9039,7 +9054,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>1999</v>
       </c>
@@ -9064,7 +9079,7 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>1999</v>
       </c>
@@ -9089,7 +9104,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1999</v>
       </c>
@@ -9114,7 +9129,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>1999</v>
       </c>
@@ -9139,7 +9154,7 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>1999</v>
       </c>
@@ -9164,7 +9179,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1999</v>
       </c>
@@ -9189,7 +9204,7 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>1999</v>
       </c>
@@ -9214,7 +9229,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>1999</v>
       </c>
@@ -9239,7 +9254,7 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>1999</v>
       </c>
@@ -9264,7 +9279,7 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>1999</v>
       </c>
@@ -9289,7 +9304,7 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>1999</v>
       </c>
@@ -9314,7 +9329,7 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2000</v>
       </c>
@@ -9339,7 +9354,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -9364,7 +9379,7 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2000</v>
       </c>
@@ -9389,7 +9404,7 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2000</v>
       </c>
@@ -9414,7 +9429,7 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2000</v>
       </c>
@@ -9439,7 +9454,7 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2000</v>
       </c>
@@ -9464,7 +9479,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>2000</v>
       </c>
@@ -9489,7 +9504,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>2000</v>
       </c>
@@ -9514,7 +9529,7 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2000</v>
       </c>
@@ -9539,7 +9554,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2000</v>
       </c>
@@ -9564,7 +9579,7 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2000</v>
       </c>
@@ -9589,7 +9604,7 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>2000</v>
       </c>
@@ -9614,7 +9629,7 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>2001</v>
       </c>
@@ -9639,7 +9654,7 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>2001</v>
       </c>
@@ -9664,7 +9679,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>2001</v>
       </c>
@@ -9689,7 +9704,7 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2001</v>
       </c>
@@ -9714,7 +9729,7 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>2001</v>
       </c>
@@ -9739,7 +9754,7 @@
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2001</v>
       </c>
@@ -9764,7 +9779,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>2001</v>
       </c>
@@ -9789,7 +9804,7 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>2001</v>
       </c>
@@ -9814,7 +9829,7 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>2001</v>
       </c>
@@ -9839,7 +9854,7 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>2001</v>
       </c>
@@ -9864,7 +9879,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>2001</v>
       </c>
@@ -9889,7 +9904,7 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>2001</v>
       </c>
@@ -9914,7 +9929,7 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>2002</v>
       </c>
@@ -9939,7 +9954,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>2002</v>
       </c>
@@ -9964,7 +9979,7 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>2002</v>
       </c>
@@ -9989,7 +10004,7 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>2002</v>
       </c>
@@ -10014,7 +10029,7 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>2002</v>
       </c>
@@ -10039,7 +10054,7 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>2002</v>
       </c>
@@ -10064,7 +10079,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>2002</v>
       </c>
@@ -10089,7 +10104,7 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>2002</v>
       </c>
@@ -10114,7 +10129,7 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>2002</v>
       </c>
@@ -10139,7 +10154,7 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>2002</v>
       </c>
@@ -10164,7 +10179,7 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>2002</v>
       </c>
@@ -10189,7 +10204,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>2002</v>
       </c>
@@ -10214,7 +10229,7 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>2003</v>
       </c>
@@ -10245,7 +10260,7 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>2003</v>
       </c>
@@ -10276,7 +10291,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>2003</v>
       </c>
@@ -10307,7 +10322,7 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>2003</v>
       </c>
@@ -10338,7 +10353,7 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>2003</v>
       </c>
@@ -10369,7 +10384,7 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>2003</v>
       </c>
@@ -10400,7 +10415,7 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>2003</v>
       </c>
@@ -10431,7 +10446,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>2003</v>
       </c>
@@ -10462,7 +10477,7 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>2003</v>
       </c>
@@ -10493,7 +10508,7 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>2003</v>
       </c>
@@ -10524,7 +10539,7 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>2003</v>
       </c>
@@ -10555,7 +10570,7 @@
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>2003</v>
       </c>
@@ -10586,7 +10601,7 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>2004</v>
       </c>
@@ -10617,7 +10632,7 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>2004</v>
       </c>
@@ -10648,7 +10663,7 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>2004</v>
       </c>
@@ -10679,7 +10694,7 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>2004</v>
       </c>
@@ -10710,7 +10725,7 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>2004</v>
       </c>
@@ -10741,7 +10756,7 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>2004</v>
       </c>
@@ -10772,7 +10787,7 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>2004</v>
       </c>
@@ -10803,7 +10818,7 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>2004</v>
       </c>
@@ -10834,7 +10849,7 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>2004</v>
       </c>
@@ -10865,7 +10880,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>2004</v>
       </c>
@@ -10896,7 +10911,7 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>2004</v>
       </c>
@@ -10927,7 +10942,7 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>2004</v>
       </c>
@@ -10958,7 +10973,7 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>2005</v>
       </c>
@@ -10989,7 +11004,7 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>2005</v>
       </c>
@@ -11020,7 +11035,7 @@
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>2005</v>
       </c>
@@ -11051,7 +11066,7 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>2005</v>
       </c>
@@ -11082,7 +11097,7 @@
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>2005</v>
       </c>
@@ -11113,7 +11128,7 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>2005</v>
       </c>
@@ -11144,7 +11159,7 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>2005</v>
       </c>
@@ -11175,7 +11190,7 @@
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>2005</v>
       </c>
@@ -11206,7 +11221,7 @@
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>2005</v>
       </c>
@@ -11237,7 +11252,7 @@
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>2005</v>
       </c>
@@ -11268,7 +11283,7 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>2005</v>
       </c>
@@ -11299,7 +11314,7 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>2005</v>
       </c>
@@ -11330,7 +11345,7 @@
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>2006</v>
       </c>
@@ -11361,7 +11376,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>2006</v>
       </c>
@@ -11392,7 +11407,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>2006</v>
       </c>
@@ -11423,7 +11438,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>2006</v>
       </c>
@@ -11454,7 +11469,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>2006</v>
       </c>
@@ -11485,7 +11500,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>2006</v>
       </c>
@@ -11516,7 +11531,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>2006</v>
       </c>
@@ -11547,7 +11562,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>2006</v>
       </c>
@@ -11578,7 +11593,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>2006</v>
       </c>
@@ -11609,7 +11624,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>2006</v>
       </c>
@@ -11640,7 +11655,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>2006</v>
       </c>
@@ -11671,7 +11686,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>2006</v>
       </c>
@@ -11702,7 +11717,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>2007</v>
       </c>
@@ -11733,7 +11748,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>2007</v>
       </c>
@@ -11764,7 +11779,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>2007</v>
       </c>
@@ -11795,7 +11810,7 @@
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>2007</v>
       </c>
@@ -11826,7 +11841,7 @@
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>2007</v>
       </c>
@@ -11857,7 +11872,7 @@
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>2007</v>
       </c>
@@ -11888,7 +11903,7 @@
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>2007</v>
       </c>
@@ -11919,7 +11934,7 @@
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>2007</v>
       </c>
@@ -11950,7 +11965,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>2007</v>
       </c>
@@ -11981,7 +11996,7 @@
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>2007</v>
       </c>
@@ -12012,7 +12027,7 @@
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>2007</v>
       </c>
@@ -12043,7 +12058,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>2007</v>
       </c>
@@ -12074,7 +12089,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>2008</v>
       </c>
@@ -12105,7 +12120,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>2008</v>
       </c>
@@ -12136,7 +12151,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>2008</v>
       </c>
@@ -12167,7 +12182,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>2008</v>
       </c>
@@ -12198,7 +12213,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>2008</v>
       </c>
@@ -12229,7 +12244,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>2008</v>
       </c>
@@ -12260,7 +12275,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>2008</v>
       </c>
@@ -12291,7 +12306,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>2008</v>
       </c>
@@ -12322,7 +12337,7 @@
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>2008</v>
       </c>
@@ -12353,7 +12368,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>2008</v>
       </c>
@@ -12384,7 +12399,7 @@
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>2008</v>
       </c>
@@ -12415,7 +12430,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>2008</v>
       </c>
@@ -12446,7 +12461,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>2009</v>
       </c>
@@ -12477,7 +12492,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>2009</v>
       </c>
@@ -12508,7 +12523,7 @@
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>2009</v>
       </c>
@@ -12539,7 +12554,7 @@
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>2009</v>
       </c>
@@ -12570,7 +12585,7 @@
       <c r="L137" s="3"/>
       <c r="M137" s="3"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>2009</v>
       </c>
@@ -12601,7 +12616,7 @@
       <c r="L138" s="3"/>
       <c r="M138" s="3"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>2009</v>
       </c>
@@ -12632,7 +12647,7 @@
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>2009</v>
       </c>
@@ -12663,7 +12678,7 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>2009</v>
       </c>
@@ -12694,7 +12709,7 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>2009</v>
       </c>
@@ -12725,7 +12740,7 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>2009</v>
       </c>
@@ -12756,7 +12771,7 @@
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>2009</v>
       </c>
@@ -12787,7 +12802,7 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>2009</v>
       </c>
@@ -12818,7 +12833,7 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>2010</v>
       </c>
@@ -12849,7 +12864,7 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>2010</v>
       </c>
@@ -12880,7 +12895,7 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>2010</v>
       </c>
@@ -12911,7 +12926,7 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>2010</v>
       </c>
@@ -12942,7 +12957,7 @@
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>2010</v>
       </c>
@@ -12973,7 +12988,7 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>2010</v>
       </c>
@@ -13004,7 +13019,7 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>2010</v>
       </c>
@@ -13035,7 +13050,7 @@
       <c r="L152" s="3"/>
       <c r="M152" s="3"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>2010</v>
       </c>
@@ -13066,7 +13081,7 @@
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>2010</v>
       </c>
@@ -13097,7 +13112,7 @@
       <c r="L154" s="3"/>
       <c r="M154" s="3"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>2010</v>
       </c>
@@ -13128,7 +13143,7 @@
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>2010</v>
       </c>
@@ -13159,7 +13174,7 @@
       <c r="L156" s="3"/>
       <c r="M156" s="3"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>2010</v>
       </c>
@@ -13190,7 +13205,7 @@
       <c r="L157" s="3"/>
       <c r="M157" s="3"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>2011</v>
       </c>
@@ -13223,7 +13238,7 @@
       </c>
       <c r="M158" s="3"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>2011</v>
       </c>
@@ -13256,7 +13271,7 @@
       </c>
       <c r="M159" s="3"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>2011</v>
       </c>
@@ -13289,7 +13304,7 @@
       </c>
       <c r="M160" s="3"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>2011</v>
       </c>
@@ -13322,7 +13337,7 @@
       </c>
       <c r="M161" s="3"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>2011</v>
       </c>
@@ -13355,7 +13370,7 @@
       </c>
       <c r="M162" s="3"/>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>2011</v>
       </c>
@@ -13388,7 +13403,7 @@
       </c>
       <c r="M163" s="3"/>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>2011</v>
       </c>
@@ -13421,7 +13436,7 @@
       </c>
       <c r="M164" s="3"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>2011</v>
       </c>
@@ -13454,7 +13469,7 @@
       </c>
       <c r="M165" s="3"/>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>2011</v>
       </c>
@@ -13487,7 +13502,7 @@
       </c>
       <c r="M166" s="3"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>2011</v>
       </c>
@@ -13520,7 +13535,7 @@
       </c>
       <c r="M167" s="3"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>2011</v>
       </c>
@@ -13553,7 +13568,7 @@
       </c>
       <c r="M168" s="3"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>2011</v>
       </c>
@@ -13586,7 +13601,7 @@
       </c>
       <c r="M169" s="3"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>2012</v>
       </c>
@@ -13619,7 +13634,7 @@
       </c>
       <c r="M170" s="3"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>2012</v>
       </c>
@@ -13652,7 +13667,7 @@
       </c>
       <c r="M171" s="3"/>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>2012</v>
       </c>
@@ -13685,7 +13700,7 @@
       </c>
       <c r="M172" s="3"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>2012</v>
       </c>
@@ -13718,7 +13733,7 @@
       </c>
       <c r="M173" s="3"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>2012</v>
       </c>
@@ -13751,7 +13766,7 @@
       </c>
       <c r="M174" s="3"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>2012</v>
       </c>
@@ -13784,7 +13799,7 @@
       </c>
       <c r="M175" s="3"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>2012</v>
       </c>
@@ -13817,7 +13832,7 @@
       </c>
       <c r="M176" s="3"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>2012</v>
       </c>
@@ -13850,7 +13865,7 @@
       </c>
       <c r="M177" s="3"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>2012</v>
       </c>
@@ -13883,7 +13898,7 @@
       </c>
       <c r="M178" s="3"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>2012</v>
       </c>
@@ -13916,7 +13931,7 @@
       </c>
       <c r="M179" s="3"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>2012</v>
       </c>
@@ -13949,7 +13964,7 @@
       </c>
       <c r="M180" s="3"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>2012</v>
       </c>
@@ -13982,7 +13997,7 @@
       </c>
       <c r="M181" s="3"/>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>2013</v>
       </c>
@@ -14015,7 +14030,7 @@
       </c>
       <c r="M182" s="3"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>2013</v>
       </c>
@@ -14048,7 +14063,7 @@
       </c>
       <c r="M183" s="3"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>2013</v>
       </c>
@@ -14081,7 +14096,7 @@
       </c>
       <c r="M184" s="3"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>2013</v>
       </c>
@@ -14114,7 +14129,7 @@
       </c>
       <c r="M185" s="3"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>2013</v>
       </c>
@@ -14147,7 +14162,7 @@
       </c>
       <c r="M186" s="3"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>2013</v>
       </c>
@@ -14180,7 +14195,7 @@
       </c>
       <c r="M187" s="3"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>2013</v>
       </c>
@@ -14213,7 +14228,7 @@
       </c>
       <c r="M188" s="3"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>2013</v>
       </c>
@@ -14246,7 +14261,7 @@
       </c>
       <c r="M189" s="3"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>2013</v>
       </c>
@@ -14279,7 +14294,7 @@
       </c>
       <c r="M190" s="3"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>2013</v>
       </c>
@@ -14312,7 +14327,7 @@
       </c>
       <c r="M191" s="3"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>2013</v>
       </c>
@@ -14345,7 +14360,7 @@
       </c>
       <c r="M192" s="3"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>2013</v>
       </c>
@@ -14378,7 +14393,7 @@
       </c>
       <c r="M193" s="3"/>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>2014</v>
       </c>
@@ -14411,7 +14426,7 @@
       </c>
       <c r="M194" s="3"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>2014</v>
       </c>
@@ -14444,7 +14459,7 @@
       </c>
       <c r="M195" s="3"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>2014</v>
       </c>
@@ -14477,7 +14492,7 @@
       </c>
       <c r="M196" s="3"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>2014</v>
       </c>
@@ -14510,7 +14525,7 @@
       </c>
       <c r="M197" s="3"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>2014</v>
       </c>
@@ -14543,7 +14558,7 @@
       </c>
       <c r="M198" s="3"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>2014</v>
       </c>
@@ -14576,7 +14591,7 @@
       </c>
       <c r="M199" s="3"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>2014</v>
       </c>
@@ -14609,7 +14624,7 @@
       </c>
       <c r="M200" s="3"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>2014</v>
       </c>
@@ -14642,7 +14657,7 @@
       </c>
       <c r="M201" s="3"/>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>2014</v>
       </c>
@@ -14675,7 +14690,7 @@
       </c>
       <c r="M202" s="3"/>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>2014</v>
       </c>
@@ -14708,7 +14723,7 @@
       </c>
       <c r="M203" s="3"/>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>2014</v>
       </c>
@@ -14741,7 +14756,7 @@
       </c>
       <c r="M204" s="3"/>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>2014</v>
       </c>
@@ -14774,7 +14789,7 @@
       </c>
       <c r="M205" s="3"/>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>2015</v>
       </c>
@@ -14809,7 +14824,7 @@
       </c>
       <c r="M206" s="3"/>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>2015</v>
       </c>
@@ -14845,7 +14860,7 @@
       </c>
       <c r="M207" s="3"/>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>2015</v>
       </c>
@@ -14881,7 +14896,7 @@
       </c>
       <c r="M208" s="3"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>2015</v>
       </c>
@@ -14917,7 +14932,7 @@
       </c>
       <c r="M209" s="3"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>2015</v>
       </c>
@@ -14953,7 +14968,7 @@
       </c>
       <c r="M210" s="3"/>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>2015</v>
       </c>
@@ -14989,7 +15004,7 @@
       </c>
       <c r="M211" s="3"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>2015</v>
       </c>
@@ -15025,7 +15040,7 @@
       </c>
       <c r="M212" s="3"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>2015</v>
       </c>
@@ -15061,7 +15076,7 @@
       </c>
       <c r="M213" s="3"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>2015</v>
       </c>
@@ -15097,7 +15112,7 @@
       </c>
       <c r="M214" s="3"/>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>2015</v>
       </c>
@@ -15133,7 +15148,7 @@
       </c>
       <c r="M215" s="3"/>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>2015</v>
       </c>
@@ -15169,7 +15184,7 @@
       </c>
       <c r="M216" s="3"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>2015</v>
       </c>
@@ -15205,7 +15220,7 @@
       </c>
       <c r="M217" s="3"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>2016</v>
       </c>
@@ -15241,7 +15256,7 @@
       </c>
       <c r="M218" s="3"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>2016</v>
       </c>
@@ -15277,7 +15292,7 @@
       </c>
       <c r="M219" s="3"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>2016</v>
       </c>
@@ -15313,7 +15328,7 @@
       </c>
       <c r="M220" s="3"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>2016</v>
       </c>
@@ -15349,7 +15364,7 @@
       </c>
       <c r="M221" s="3"/>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>2016</v>
       </c>
@@ -15385,7 +15400,7 @@
       </c>
       <c r="M222" s="3"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>2016</v>
       </c>
@@ -15421,7 +15436,7 @@
       </c>
       <c r="M223" s="3"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>2016</v>
       </c>
@@ -15457,7 +15472,7 @@
       </c>
       <c r="M224" s="3"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>2016</v>
       </c>
@@ -15493,7 +15508,7 @@
       </c>
       <c r="M225" s="3"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>2016</v>
       </c>
@@ -15529,7 +15544,7 @@
       </c>
       <c r="M226" s="3"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>2016</v>
       </c>
@@ -15565,7 +15580,7 @@
       </c>
       <c r="M227" s="3"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>2016</v>
       </c>
@@ -15601,7 +15616,7 @@
       </c>
       <c r="M228" s="3"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>2016</v>
       </c>
@@ -15637,7 +15652,7 @@
       </c>
       <c r="M229" s="3"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>2017</v>
       </c>
@@ -15679,7 +15694,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>2017</v>
       </c>
@@ -15721,7 +15736,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>2017</v>
       </c>
@@ -15763,7 +15778,7 @@
         <v>2.8039999999999998</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>2017</v>
       </c>
@@ -15805,7 +15820,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>2017</v>
       </c>
@@ -15847,7 +15862,7 @@
         <v>2.8839999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>2017</v>
       </c>
@@ -15889,7 +15904,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>2017</v>
       </c>
@@ -15931,7 +15946,7 @@
         <v>3.069</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>2017</v>
       </c>
@@ -15973,7 +15988,7 @@
         <v>3.052</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>2017</v>
       </c>
@@ -16015,7 +16030,7 @@
         <v>3.1309999999999998</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>2017</v>
       </c>
@@ -16057,7 +16072,7 @@
         <v>3.157</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>2017</v>
       </c>
@@ -16099,7 +16114,7 @@
         <v>3.1669999999999998</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>2017</v>
       </c>
@@ -16141,7 +16156,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>2018</v>
       </c>
@@ -16183,7 +16198,7 @@
         <v>2.8159999999999998</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>2018</v>
       </c>
@@ -16225,7 +16240,7 @@
         <v>2.7549999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>2018</v>
       </c>
@@ -16267,7 +16282,7 @@
         <v>2.762</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>2018</v>
       </c>
@@ -16309,7 +16324,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>2018</v>
       </c>
@@ -16351,7 +16366,7 @@
         <v>2.952</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>2018</v>
       </c>
@@ -16393,7 +16408,7 @@
         <v>3.0350000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>2018</v>
       </c>
@@ -16435,7 +16450,7 @@
         <v>3.085</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>2018</v>
       </c>
@@ -16477,7 +16492,7 @@
         <v>3.1659999999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>2018</v>
       </c>
@@ -16519,7 +16534,7 @@
         <v>3.0880000000000001</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>2018</v>
       </c>
@@ -16561,7 +16576,7 @@
         <v>3.105</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>2018</v>
       </c>
@@ -16603,7 +16618,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>2018</v>
       </c>
@@ -16645,7 +16660,7 @@
         <v>2.9950229617784081</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>2019</v>
       </c>
@@ -16687,7 +16702,7 @@
         <v>2.9209999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>2019</v>
       </c>
@@ -16729,7 +16744,7 @@
         <v>2.9689999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>2019</v>
       </c>
@@ -16771,7 +16786,7 @@
         <v>2.9430000000000001</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>2019</v>
       </c>
@@ -16813,7 +16828,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>2019</v>
       </c>
@@ -16855,7 +16870,7 @@
         <v>3.121</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>2019</v>
       </c>
@@ -16897,7 +16912,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>2019</v>
       </c>
@@ -16939,7 +16954,7 @@
         <v>3.431</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>2019</v>
       </c>
@@ -16981,7 +16996,7 @@
         <v>3.4119999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>2019</v>
       </c>
@@ -17023,7 +17038,7 @@
         <v>3.613</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>2019</v>
       </c>
@@ -17065,7 +17080,7 @@
         <v>3.827</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>2019</v>
       </c>
@@ -17107,7 +17122,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>2019</v>
       </c>
@@ -17149,7 +17164,7 @@
         <v>3.9329999999999998</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>2020</v>
       </c>
@@ -17191,7 +17206,7 @@
         <v>3.6349999999999998</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>2020</v>
       </c>
@@ -17233,7 +17248,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>2020</v>
       </c>
@@ -17275,7 +17290,7 @@
         <v>3.234</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>2020</v>
       </c>
@@ -17317,7 +17332,7 @@
         <v>3.202</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>2020</v>
       </c>
@@ -17359,7 +17374,7 @@
         <v>3.0590000000000002</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>2020</v>
       </c>
@@ -17401,7 +17416,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>2020</v>
       </c>
@@ -17443,7 +17458,7 @@
         <v>3.0859999999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>2020</v>
       </c>
@@ -17485,7 +17500,7 @@
         <v>3.0609999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>2020</v>
       </c>
@@ -17527,7 +17542,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>2020</v>
       </c>
@@ -17569,7 +17584,7 @@
         <v>3.093</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>2020</v>
       </c>
@@ -17611,7 +17626,7 @@
         <v>2.9820000000000002</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>2020</v>
       </c>
@@ -17653,7 +17668,7 @@
         <v>2.8410000000000002</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>2021</v>
       </c>
@@ -17694,7 +17709,7 @@
         <v>2.8530000000000002</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>2021</v>
       </c>
@@ -17736,7 +17751,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>2021</v>
       </c>
@@ -17778,7 +17793,7 @@
         <v>3.1920000000000002</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>2021</v>
       </c>
@@ -17820,7 +17835,7 @@
         <v>3.3559999999999999</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>2021</v>
       </c>
@@ -17862,7 +17877,7 @@
         <v>3.6019999999999999</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>2021</v>
       </c>
@@ -17904,7 +17919,7 @@
         <v>3.8460000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>2021</v>
       </c>
@@ -17946,7 +17961,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>2021</v>
       </c>
@@ -17988,7 +18003,7 @@
         <v>4.2069999999999999</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>2021</v>
       </c>
@@ -18030,7 +18045,7 @@
         <v>4.3579999999999997</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>2021</v>
       </c>
@@ -18072,7 +18087,7 @@
         <v>4.4829999999999997</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>2021</v>
       </c>
@@ -18114,7 +18129,7 @@
         <v>4.3630000000000004</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>2021</v>
       </c>
@@ -18156,7 +18171,7 @@
         <v>3.9740000000000002</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>2022</v>
       </c>
@@ -18198,7 +18213,7 @@
         <v>3.6070000000000002</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>2022</v>
       </c>
@@ -18240,7 +18255,7 @@
         <v>3.6589999999999998</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>2022</v>
       </c>
@@ -18282,7 +18297,7 @@
         <v>3.964</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>2022</v>
       </c>
@@ -18324,7 +18339,7 @@
         <v>4.0640000000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>2022</v>
       </c>
@@ -18363,7 +18378,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>2022</v>
       </c>
@@ -18402,7 +18417,7 @@
         <v>4.1920000000000002</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>2022</v>
       </c>
@@ -18441,7 +18456,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>2022</v>
       </c>
@@ -18480,7 +18495,7 @@
         <v>4.2949999999999999</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>2022</v>
       </c>
@@ -18519,7 +18534,7 @@
         <v>4.0940000000000003</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>2022</v>
       </c>
@@ -18558,7 +18573,7 @@
         <v>3.1629999999999998</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>2022</v>
       </c>
@@ -18597,7 +18612,7 @@
         <v>2.6560000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>2022</v>
       </c>
@@ -18636,7 +18651,7 @@
         <v>2.536</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>2023</v>
       </c>
@@ -18675,7 +18690,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>2023</v>
       </c>
@@ -18714,7 +18729,7 @@
         <v>2.7469999999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>2023</v>
       </c>
@@ -18753,7 +18768,7 @@
         <v>2.9980000000000002</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>2023</v>
       </c>
@@ -18792,7 +18807,7 @@
         <v>3.1240000000000001</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>2023</v>
       </c>
@@ -18831,7 +18846,7 @@
         <v>2.8090000000000002</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>2023</v>
       </c>
@@ -18870,7 +18885,7 @@
         <v>2.5579999999999998</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>2023</v>
       </c>
@@ -18909,7 +18924,7 @@
         <v>2.532</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>2023</v>
       </c>
@@ -18948,7 +18963,7 @@
         <v>2.3969999999999998</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>2023</v>
       </c>
@@ -18987,7 +19002,7 @@
         <v>2.4319999999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>2023</v>
       </c>
@@ -19026,7 +19041,7 @@
         <v>2.3809999999999998</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>2023</v>
       </c>
@@ -19065,7 +19080,7 @@
         <v>2.2029999999999998</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>2023</v>
       </c>
@@ -19104,7 +19119,7 @@
         <v>2.1920000000000002</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>2024</v>
       </c>
@@ -19143,7 +19158,7 @@
         <v>2.274</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>2024</v>
       </c>
@@ -19182,7 +19197,7 @@
         <v>2.4620000000000002</v>
       </c>
     </row>
-    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>2024</v>
       </c>
@@ -19221,7 +19236,7 @@
         <v>2.5350000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>2024</v>
       </c>
@@ -19260,7 +19275,7 @@
         <v>2.7410000000000001</v>
       </c>
     </row>
-    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>2024</v>
       </c>
@@ -19299,7 +19314,7 @@
         <v>2.7930000000000001</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>2024</v>
       </c>
@@ -19338,7 +19353,7 @@
         <v>2.9889999999999999</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>2024</v>
       </c>
@@ -19377,7 +19392,7 @@
         <v>3.1110000000000002</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>2024</v>
       </c>
@@ -19416,7 +19431,7 @@
         <v>3.1850000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>2024</v>
       </c>
@@ -19455,7 +19470,7 @@
         <v>3.1419999999999999</v>
       </c>
     </row>
-    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>2024</v>
       </c>
@@ -19494,7 +19509,7 @@
         <v>3.2509999999999999</v>
       </c>
     </row>
-    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>2024</v>
       </c>
@@ -19533,7 +19548,7 @@
         <v>3.2970000000000002</v>
       </c>
     </row>
-    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>2024</v>
       </c>
@@ -19572,7 +19587,7 @@
         <v>3.2309999999999999</v>
       </c>
     </row>
-    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>2025</v>
       </c>
@@ -19611,7 +19626,7 @@
         <v>3.3580000000000001</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>2025</v>
       </c>
@@ -19650,7 +19665,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>2025</v>
       </c>
@@ -19689,7 +19704,7 @@
         <v>3.5249999999999999</v>
       </c>
     </row>
-    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>2025</v>
       </c>
@@ -19728,7 +19743,7 @@
         <v>3.496</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>2025</v>
       </c>
@@ -19767,7 +19782,7 @@
         <v>3.5640000000000001</v>
       </c>
     </row>
-    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>2025</v>
       </c>
@@ -19806,7 +19821,7 @@
         <v>3.6320000000000001</v>
       </c>
     </row>
-    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>2025</v>
       </c>
@@ -19845,7 +19860,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>2025</v>
       </c>
@@ -19884,7 +19899,7 @@
         <v>4.3029999999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>2025</v>
       </c>
@@ -19923,7 +19938,7 @@
         <v>4.4409999999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>2025</v>
       </c>
@@ -19962,7 +19977,7 @@
         <v>4.7690000000000001</v>
       </c>
     </row>
-    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>2025</v>
       </c>
@@ -20001,7 +20016,7 @@
         <v>4.8339999999999996</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>2025</v>
       </c>
@@ -20040,7 +20055,7 @@
         <v>4.6840000000000002</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>2026</v>
       </c>
@@ -20079,7 +20094,7 @@
         <v>4.6260000000000003</v>
       </c>
     </row>
-    <row r="339" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>2026</v>
       </c>
@@ -20118,7 +20133,7 @@
         <v>4.7889999999999997</v>
       </c>
     </row>
-    <row r="340" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <v>2026</v>
       </c>
@@ -20157,7 +20172,7 @@
         <v>4.8490000000000002</v>
       </c>
     </row>
-    <row r="341" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>2026</v>
       </c>
@@ -20196,7 +20211,7 @@
         <v>4.8470000000000004</v>
       </c>
     </row>
-    <row r="342" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>2026</v>
       </c>
@@ -20233,6 +20248,45 @@
       </c>
       <c r="M342" s="3">
         <v>5.12</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A343" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B343" s="18"/>
+      <c r="C343" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D343" s="1">
+        <v>3.1659999999999999</v>
+      </c>
+      <c r="E343" s="3">
+        <v>5.7450000000000001</v>
+      </c>
+      <c r="F343" s="3">
+        <v>5.694</v>
+      </c>
+      <c r="G343" s="1">
+        <v>2.6890000000000001</v>
+      </c>
+      <c r="H343" s="3">
+        <v>5.3079999999999998</v>
+      </c>
+      <c r="I343" s="1">
+        <v>3.093</v>
+      </c>
+      <c r="J343" s="3">
+        <v>5.6779999999999999</v>
+      </c>
+      <c r="K343" s="3">
+        <v>5.5709999999999997</v>
+      </c>
+      <c r="L343" s="3">
+        <v>6.2750000000000004</v>
+      </c>
+      <c r="M343" s="3">
+        <v>5.0919999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/precios_hacienda_inac.xlsx
+++ b/data_raw/precios_hacienda_inac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GIF\Análisis sectorial\Indicadores y Precios\Precios Hacienda\SERIES DE PRECIOS SEMANALES Y MENSUALES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6228876A-811C-4C5B-90F6-5567191AA717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2429E6DB-4AD1-4974-BCE1-75C33430A22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HACIENDA" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Cordero Gancho" sheetId="11" r:id="rId5"/>
     <sheet name="Oveja Gancho" sheetId="12" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0" concurrentManualCount="4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="36">
   <si>
     <t>Ene</t>
   </si>
@@ -326,7 +326,7 @@
     <numFmt numFmtId="165" formatCode="[$-C0A]mmmm\-yy;@"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,6 +580,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1440,7 +1446,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$344</c:f>
+              <c:f>HACIENDA!$E$345</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1889,10 +1895,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$E$338:$E$343</c:f>
+              <c:f>HACIENDA!$E$338:$E$344</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>5.37</c:v>
                 </c:pt>
@@ -1910,6 +1916,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>5.7450000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.851</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3016,7 +3025,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$343</c:f>
+              <c:f>HACIENDA!$A$344</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3090,10 +3099,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$H$338:$H$343</c:f>
+              <c:f>HACIENDA!$H$338:$H$344</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>4.9130000000000003</c:v>
                 </c:pt>
@@ -3111,6 +3120,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>5.3079999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.3369999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4212,7 +4224,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$343</c:f>
+              <c:f>HACIENDA!$A$344</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4286,10 +4298,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338:$J$343</c:f>
+              <c:f>HACIENDA!$J$338:$J$344</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>5.25</c:v>
                 </c:pt>
@@ -4307,6 +4319,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>5.6779999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.7880000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5384,7 +5399,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$343</c:f>
+              <c:f>HACIENDA!$A$344</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5458,10 +5473,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$J$338:$J$343</c:f>
+              <c:f>HACIENDA!$J$338:$J$344</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>5.25</c:v>
                 </c:pt>
@@ -5479,6 +5494,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>5.6779999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.7880000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6556,7 +6574,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>HACIENDA!$A$343</c:f>
+              <c:f>HACIENDA!$A$344</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6621,10 +6639,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HACIENDA!$M$338:$M$343</c:f>
+              <c:f>HACIENDA!$M$338:$M$344</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>4.6260000000000003</c:v>
                 </c:pt>
@@ -6642,6 +6660,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>5.0919999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.1100000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8265,7 +8286,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9286875" cy="6048375"/>
+    <xdr:ext cx="9283700" cy="6045200"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="1 Gráfico">
@@ -8832,21 +8853,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M343"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M344"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" hidden="1" customWidth="1"/>
-    <col min="3" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" customWidth="1"/>
-    <col min="12" max="13" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" hidden="1" customWidth="1"/>
+    <col min="3" max="5" width="11.54296875" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" customWidth="1"/>
+    <col min="7" max="9" width="11.54296875" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" customWidth="1"/>
+    <col min="12" max="13" width="11.54296875" customWidth="1"/>
     <col min="14" max="14" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
@@ -8862,7 +8883,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
       <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
@@ -8876,44 +8897,44 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D4" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D6" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C7" s="19"/>
       <c r="D7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="19"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D8" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D9" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
         <v>22</v>
       </c>
@@ -8946,7 +8967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="27.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="27.5" x14ac:dyDescent="0.35">
       <c r="A11" s="20"/>
       <c r="B11" s="16" t="s">
         <v>35</v>
@@ -8983,7 +9004,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>1998</v>
       </c>
@@ -9006,7 +9027,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>1998</v>
       </c>
@@ -9029,7 +9050,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>1999</v>
       </c>
@@ -9054,7 +9075,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>1999</v>
       </c>
@@ -9079,7 +9100,7 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>1999</v>
       </c>
@@ -9104,7 +9125,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>1999</v>
       </c>
@@ -9129,7 +9150,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>1999</v>
       </c>
@@ -9154,7 +9175,7 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>1999</v>
       </c>
@@ -9179,7 +9200,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>1999</v>
       </c>
@@ -9204,7 +9225,7 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>1999</v>
       </c>
@@ -9229,7 +9250,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>1999</v>
       </c>
@@ -9254,7 +9275,7 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>1999</v>
       </c>
@@ -9279,7 +9300,7 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>1999</v>
       </c>
@@ -9304,7 +9325,7 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>1999</v>
       </c>
@@ -9329,7 +9350,7 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2000</v>
       </c>
@@ -9354,7 +9375,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -9379,7 +9400,7 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2000</v>
       </c>
@@ -9404,7 +9425,7 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2000</v>
       </c>
@@ -9429,7 +9450,7 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2000</v>
       </c>
@@ -9454,7 +9475,7 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2000</v>
       </c>
@@ -9479,7 +9500,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2000</v>
       </c>
@@ -9504,7 +9525,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2000</v>
       </c>
@@ -9529,7 +9550,7 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2000</v>
       </c>
@@ -9554,7 +9575,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2000</v>
       </c>
@@ -9579,7 +9600,7 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2000</v>
       </c>
@@ -9604,7 +9625,7 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2000</v>
       </c>
@@ -9629,7 +9650,7 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2001</v>
       </c>
@@ -9654,7 +9675,7 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2001</v>
       </c>
@@ -9679,7 +9700,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2001</v>
       </c>
@@ -9704,7 +9725,7 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2001</v>
       </c>
@@ -9729,7 +9750,7 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>2001</v>
       </c>
@@ -9754,7 +9775,7 @@
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>2001</v>
       </c>
@@ -9779,7 +9800,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>2001</v>
       </c>
@@ -9804,7 +9825,7 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>2001</v>
       </c>
@@ -9829,7 +9850,7 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>2001</v>
       </c>
@@ -9854,7 +9875,7 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>2001</v>
       </c>
@@ -9879,7 +9900,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>2001</v>
       </c>
@@ -9904,7 +9925,7 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>2001</v>
       </c>
@@ -9929,7 +9950,7 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>2002</v>
       </c>
@@ -9954,7 +9975,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>2002</v>
       </c>
@@ -9979,7 +10000,7 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>2002</v>
       </c>
@@ -10004,7 +10025,7 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>2002</v>
       </c>
@@ -10029,7 +10050,7 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>2002</v>
       </c>
@@ -10054,7 +10075,7 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2002</v>
       </c>
@@ -10079,7 +10100,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2002</v>
       </c>
@@ -10104,7 +10125,7 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2002</v>
       </c>
@@ -10129,7 +10150,7 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2002</v>
       </c>
@@ -10154,7 +10175,7 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2002</v>
       </c>
@@ -10179,7 +10200,7 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2002</v>
       </c>
@@ -10204,7 +10225,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2002</v>
       </c>
@@ -10229,7 +10250,7 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2003</v>
       </c>
@@ -10260,7 +10281,7 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2003</v>
       </c>
@@ -10291,7 +10312,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2003</v>
       </c>
@@ -10322,7 +10343,7 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2003</v>
       </c>
@@ -10353,7 +10374,7 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2003</v>
       </c>
@@ -10384,7 +10405,7 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2003</v>
       </c>
@@ -10415,7 +10436,7 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2003</v>
       </c>
@@ -10446,7 +10467,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2003</v>
       </c>
@@ -10477,7 +10498,7 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>2003</v>
       </c>
@@ -10508,7 +10529,7 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2003</v>
       </c>
@@ -10539,7 +10560,7 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2003</v>
       </c>
@@ -10570,7 +10591,7 @@
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>2003</v>
       </c>
@@ -10601,7 +10622,7 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>2004</v>
       </c>
@@ -10632,7 +10653,7 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2004</v>
       </c>
@@ -10663,7 +10684,7 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>2004</v>
       </c>
@@ -10694,7 +10715,7 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2004</v>
       </c>
@@ -10725,7 +10746,7 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2004</v>
       </c>
@@ -10756,7 +10777,7 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2004</v>
       </c>
@@ -10787,7 +10808,7 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2004</v>
       </c>
@@ -10818,7 +10839,7 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2004</v>
       </c>
@@ -10849,7 +10870,7 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2004</v>
       </c>
@@ -10880,7 +10901,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>2004</v>
       </c>
@@ -10911,7 +10932,7 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2004</v>
       </c>
@@ -10942,7 +10963,7 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2004</v>
       </c>
@@ -10973,7 +10994,7 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2005</v>
       </c>
@@ -11004,7 +11025,7 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2005</v>
       </c>
@@ -11035,7 +11056,7 @@
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2005</v>
       </c>
@@ -11066,7 +11087,7 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>2005</v>
       </c>
@@ -11097,7 +11118,7 @@
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2005</v>
       </c>
@@ -11128,7 +11149,7 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2005</v>
       </c>
@@ -11159,7 +11180,7 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>2005</v>
       </c>
@@ -11190,7 +11211,7 @@
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>2005</v>
       </c>
@@ -11221,7 +11242,7 @@
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>2005</v>
       </c>
@@ -11252,7 +11273,7 @@
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2005</v>
       </c>
@@ -11283,7 +11304,7 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2005</v>
       </c>
@@ -11314,7 +11335,7 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>2005</v>
       </c>
@@ -11345,7 +11366,7 @@
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2006</v>
       </c>
@@ -11376,7 +11397,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2006</v>
       </c>
@@ -11407,7 +11428,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2006</v>
       </c>
@@ -11438,7 +11459,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2006</v>
       </c>
@@ -11469,7 +11490,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2006</v>
       </c>
@@ -11500,7 +11521,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2006</v>
       </c>
@@ -11531,7 +11552,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>2006</v>
       </c>
@@ -11562,7 +11583,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2006</v>
       </c>
@@ -11593,7 +11614,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>2006</v>
       </c>
@@ -11624,7 +11645,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>2006</v>
       </c>
@@ -11655,7 +11676,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2006</v>
       </c>
@@ -11686,7 +11707,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>2006</v>
       </c>
@@ -11717,7 +11738,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>2007</v>
       </c>
@@ -11748,7 +11769,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2007</v>
       </c>
@@ -11779,7 +11800,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>2007</v>
       </c>
@@ -11810,7 +11831,7 @@
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2007</v>
       </c>
@@ -11841,7 +11862,7 @@
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2007</v>
       </c>
@@ -11872,7 +11893,7 @@
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>2007</v>
       </c>
@@ -11903,7 +11924,7 @@
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2007</v>
       </c>
@@ -11934,7 +11955,7 @@
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>2007</v>
       </c>
@@ -11965,7 +11986,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>2007</v>
       </c>
@@ -11996,7 +12017,7 @@
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>2007</v>
       </c>
@@ -12027,7 +12048,7 @@
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>2007</v>
       </c>
@@ -12058,7 +12079,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>2007</v>
       </c>
@@ -12089,7 +12110,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>2008</v>
       </c>
@@ -12120,7 +12141,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>2008</v>
       </c>
@@ -12151,7 +12172,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>2008</v>
       </c>
@@ -12182,7 +12203,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>2008</v>
       </c>
@@ -12213,7 +12234,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>2008</v>
       </c>
@@ -12244,7 +12265,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>2008</v>
       </c>
@@ -12275,7 +12296,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>2008</v>
       </c>
@@ -12306,7 +12327,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>2008</v>
       </c>
@@ -12337,7 +12358,7 @@
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>2008</v>
       </c>
@@ -12368,7 +12389,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>2008</v>
       </c>
@@ -12399,7 +12420,7 @@
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>2008</v>
       </c>
@@ -12430,7 +12451,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>2008</v>
       </c>
@@ -12461,7 +12482,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>2009</v>
       </c>
@@ -12492,7 +12513,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>2009</v>
       </c>
@@ -12523,7 +12544,7 @@
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>2009</v>
       </c>
@@ -12554,7 +12575,7 @@
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>2009</v>
       </c>
@@ -12585,7 +12606,7 @@
       <c r="L137" s="3"/>
       <c r="M137" s="3"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>2009</v>
       </c>
@@ -12616,7 +12637,7 @@
       <c r="L138" s="3"/>
       <c r="M138" s="3"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>2009</v>
       </c>
@@ -12647,7 +12668,7 @@
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>2009</v>
       </c>
@@ -12678,7 +12699,7 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>2009</v>
       </c>
@@ -12709,7 +12730,7 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>2009</v>
       </c>
@@ -12740,7 +12761,7 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>2009</v>
       </c>
@@ -12771,7 +12792,7 @@
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>2009</v>
       </c>
@@ -12802,7 +12823,7 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>2009</v>
       </c>
@@ -12833,7 +12854,7 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>2010</v>
       </c>
@@ -12864,7 +12885,7 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>2010</v>
       </c>
@@ -12895,7 +12916,7 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>2010</v>
       </c>
@@ -12926,7 +12947,7 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>2010</v>
       </c>
@@ -12957,7 +12978,7 @@
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>2010</v>
       </c>
@@ -12988,7 +13009,7 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>2010</v>
       </c>
@@ -13019,7 +13040,7 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>2010</v>
       </c>
@@ -13050,7 +13071,7 @@
       <c r="L152" s="3"/>
       <c r="M152" s="3"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>2010</v>
       </c>
@@ -13081,7 +13102,7 @@
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>2010</v>
       </c>
@@ -13112,7 +13133,7 @@
       <c r="L154" s="3"/>
       <c r="M154" s="3"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>2010</v>
       </c>
@@ -13143,7 +13164,7 @@
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>2010</v>
       </c>
@@ -13174,7 +13195,7 @@
       <c r="L156" s="3"/>
       <c r="M156" s="3"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>2010</v>
       </c>
@@ -13205,7 +13226,7 @@
       <c r="L157" s="3"/>
       <c r="M157" s="3"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>2011</v>
       </c>
@@ -13238,7 +13259,7 @@
       </c>
       <c r="M158" s="3"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>2011</v>
       </c>
@@ -13271,7 +13292,7 @@
       </c>
       <c r="M159" s="3"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>2011</v>
       </c>
@@ -13304,7 +13325,7 @@
       </c>
       <c r="M160" s="3"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>2011</v>
       </c>
@@ -13337,7 +13358,7 @@
       </c>
       <c r="M161" s="3"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>2011</v>
       </c>
@@ -13370,7 +13391,7 @@
       </c>
       <c r="M162" s="3"/>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>2011</v>
       </c>
@@ -13403,7 +13424,7 @@
       </c>
       <c r="M163" s="3"/>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>2011</v>
       </c>
@@ -13436,7 +13457,7 @@
       </c>
       <c r="M164" s="3"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>2011</v>
       </c>
@@ -13469,7 +13490,7 @@
       </c>
       <c r="M165" s="3"/>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>2011</v>
       </c>
@@ -13502,7 +13523,7 @@
       </c>
       <c r="M166" s="3"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>2011</v>
       </c>
@@ -13535,7 +13556,7 @@
       </c>
       <c r="M167" s="3"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>2011</v>
       </c>
@@ -13568,7 +13589,7 @@
       </c>
       <c r="M168" s="3"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>2011</v>
       </c>
@@ -13601,7 +13622,7 @@
       </c>
       <c r="M169" s="3"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>2012</v>
       </c>
@@ -13634,7 +13655,7 @@
       </c>
       <c r="M170" s="3"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>2012</v>
       </c>
@@ -13667,7 +13688,7 @@
       </c>
       <c r="M171" s="3"/>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>2012</v>
       </c>
@@ -13700,7 +13721,7 @@
       </c>
       <c r="M172" s="3"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>2012</v>
       </c>
@@ -13733,7 +13754,7 @@
       </c>
       <c r="M173" s="3"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>2012</v>
       </c>
@@ -13766,7 +13787,7 @@
       </c>
       <c r="M174" s="3"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>2012</v>
       </c>
@@ -13799,7 +13820,7 @@
       </c>
       <c r="M175" s="3"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>2012</v>
       </c>
@@ -13832,7 +13853,7 @@
       </c>
       <c r="M176" s="3"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>2012</v>
       </c>
@@ -13865,7 +13886,7 @@
       </c>
       <c r="M177" s="3"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>2012</v>
       </c>
@@ -13898,7 +13919,7 @@
       </c>
       <c r="M178" s="3"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>2012</v>
       </c>
@@ -13931,7 +13952,7 @@
       </c>
       <c r="M179" s="3"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>2012</v>
       </c>
@@ -13964,7 +13985,7 @@
       </c>
       <c r="M180" s="3"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>2012</v>
       </c>
@@ -13997,7 +14018,7 @@
       </c>
       <c r="M181" s="3"/>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>2013</v>
       </c>
@@ -14030,7 +14051,7 @@
       </c>
       <c r="M182" s="3"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>2013</v>
       </c>
@@ -14063,7 +14084,7 @@
       </c>
       <c r="M183" s="3"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>2013</v>
       </c>
@@ -14096,7 +14117,7 @@
       </c>
       <c r="M184" s="3"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>2013</v>
       </c>
@@ -14129,7 +14150,7 @@
       </c>
       <c r="M185" s="3"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>2013</v>
       </c>
@@ -14162,7 +14183,7 @@
       </c>
       <c r="M186" s="3"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>2013</v>
       </c>
@@ -14195,7 +14216,7 @@
       </c>
       <c r="M187" s="3"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>2013</v>
       </c>
@@ -14228,7 +14249,7 @@
       </c>
       <c r="M188" s="3"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>2013</v>
       </c>
@@ -14261,7 +14282,7 @@
       </c>
       <c r="M189" s="3"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>2013</v>
       </c>
@@ -14294,7 +14315,7 @@
       </c>
       <c r="M190" s="3"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>2013</v>
       </c>
@@ -14327,7 +14348,7 @@
       </c>
       <c r="M191" s="3"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>2013</v>
       </c>
@@ -14360,7 +14381,7 @@
       </c>
       <c r="M192" s="3"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>2013</v>
       </c>
@@ -14393,7 +14414,7 @@
       </c>
       <c r="M193" s="3"/>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>2014</v>
       </c>
@@ -14426,7 +14447,7 @@
       </c>
       <c r="M194" s="3"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>2014</v>
       </c>
@@ -14459,7 +14480,7 @@
       </c>
       <c r="M195" s="3"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>2014</v>
       </c>
@@ -14492,7 +14513,7 @@
       </c>
       <c r="M196" s="3"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>2014</v>
       </c>
@@ -14525,7 +14546,7 @@
       </c>
       <c r="M197" s="3"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>2014</v>
       </c>
@@ -14558,7 +14579,7 @@
       </c>
       <c r="M198" s="3"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>2014</v>
       </c>
@@ -14591,7 +14612,7 @@
       </c>
       <c r="M199" s="3"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>2014</v>
       </c>
@@ -14624,7 +14645,7 @@
       </c>
       <c r="M200" s="3"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>2014</v>
       </c>
@@ -14657,7 +14678,7 @@
       </c>
       <c r="M201" s="3"/>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>2014</v>
       </c>
@@ -14690,7 +14711,7 @@
       </c>
       <c r="M202" s="3"/>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>2014</v>
       </c>
@@ -14723,7 +14744,7 @@
       </c>
       <c r="M203" s="3"/>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>2014</v>
       </c>
@@ -14756,7 +14777,7 @@
       </c>
       <c r="M204" s="3"/>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>2014</v>
       </c>
@@ -14789,7 +14810,7 @@
       </c>
       <c r="M205" s="3"/>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>2015</v>
       </c>
@@ -14824,7 +14845,7 @@
       </c>
       <c r="M206" s="3"/>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>2015</v>
       </c>
@@ -14860,7 +14881,7 @@
       </c>
       <c r="M207" s="3"/>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>2015</v>
       </c>
@@ -14896,7 +14917,7 @@
       </c>
       <c r="M208" s="3"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>2015</v>
       </c>
@@ -14932,7 +14953,7 @@
       </c>
       <c r="M209" s="3"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>2015</v>
       </c>
@@ -14968,7 +14989,7 @@
       </c>
       <c r="M210" s="3"/>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>2015</v>
       </c>
@@ -15004,7 +15025,7 @@
       </c>
       <c r="M211" s="3"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>2015</v>
       </c>
@@ -15040,7 +15061,7 @@
       </c>
       <c r="M212" s="3"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>2015</v>
       </c>
@@ -15076,7 +15097,7 @@
       </c>
       <c r="M213" s="3"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>2015</v>
       </c>
@@ -15112,7 +15133,7 @@
       </c>
       <c r="M214" s="3"/>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>2015</v>
       </c>
@@ -15148,7 +15169,7 @@
       </c>
       <c r="M215" s="3"/>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>2015</v>
       </c>
@@ -15184,7 +15205,7 @@
       </c>
       <c r="M216" s="3"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>2015</v>
       </c>
@@ -15220,7 +15241,7 @@
       </c>
       <c r="M217" s="3"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>2016</v>
       </c>
@@ -15256,7 +15277,7 @@
       </c>
       <c r="M218" s="3"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>2016</v>
       </c>
@@ -15292,7 +15313,7 @@
       </c>
       <c r="M219" s="3"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>2016</v>
       </c>
@@ -15328,7 +15349,7 @@
       </c>
       <c r="M220" s="3"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>2016</v>
       </c>
@@ -15364,7 +15385,7 @@
       </c>
       <c r="M221" s="3"/>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>2016</v>
       </c>
@@ -15400,7 +15421,7 @@
       </c>
       <c r="M222" s="3"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>2016</v>
       </c>
@@ -15436,7 +15457,7 @@
       </c>
       <c r="M223" s="3"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>2016</v>
       </c>
@@ -15472,7 +15493,7 @@
       </c>
       <c r="M224" s="3"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>2016</v>
       </c>
@@ -15508,7 +15529,7 @@
       </c>
       <c r="M225" s="3"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>2016</v>
       </c>
@@ -15544,7 +15565,7 @@
       </c>
       <c r="M226" s="3"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>2016</v>
       </c>
@@ -15580,7 +15601,7 @@
       </c>
       <c r="M227" s="3"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>2016</v>
       </c>
@@ -15616,7 +15637,7 @@
       </c>
       <c r="M228" s="3"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>2016</v>
       </c>
@@ -15652,7 +15673,7 @@
       </c>
       <c r="M229" s="3"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>2017</v>
       </c>
@@ -15694,7 +15715,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>2017</v>
       </c>
@@ -15736,7 +15757,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>2017</v>
       </c>
@@ -15778,7 +15799,7 @@
         <v>2.8039999999999998</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>2017</v>
       </c>
@@ -15820,7 +15841,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>2017</v>
       </c>
@@ -15862,7 +15883,7 @@
         <v>2.8839999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>2017</v>
       </c>
@@ -15904,7 +15925,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>2017</v>
       </c>
@@ -15946,7 +15967,7 @@
         <v>3.069</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>2017</v>
       </c>
@@ -15988,7 +16009,7 @@
         <v>3.052</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>2017</v>
       </c>
@@ -16030,7 +16051,7 @@
         <v>3.1309999999999998</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>2017</v>
       </c>
@@ -16072,7 +16093,7 @@
         <v>3.157</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>2017</v>
       </c>
@@ -16114,7 +16135,7 @@
         <v>3.1669999999999998</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>2017</v>
       </c>
@@ -16156,7 +16177,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>2018</v>
       </c>
@@ -16198,7 +16219,7 @@
         <v>2.8159999999999998</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>2018</v>
       </c>
@@ -16240,7 +16261,7 @@
         <v>2.7549999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>2018</v>
       </c>
@@ -16282,7 +16303,7 @@
         <v>2.762</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A245" s="2">
         <v>2018</v>
       </c>
@@ -16324,7 +16345,7 @@
         <v>2.7890000000000001</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A246" s="2">
         <v>2018</v>
       </c>
@@ -16366,7 +16387,7 @@
         <v>2.952</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A247" s="2">
         <v>2018</v>
       </c>
@@ -16408,7 +16429,7 @@
         <v>3.0350000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A248" s="2">
         <v>2018</v>
       </c>
@@ -16450,7 +16471,7 @@
         <v>3.085</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A249" s="2">
         <v>2018</v>
       </c>
@@ -16492,7 +16513,7 @@
         <v>3.1659999999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A250" s="2">
         <v>2018</v>
       </c>
@@ -16534,7 +16555,7 @@
         <v>3.0880000000000001</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A251" s="2">
         <v>2018</v>
       </c>
@@ -16576,7 +16597,7 @@
         <v>3.105</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A252" s="2">
         <v>2018</v>
       </c>
@@ -16618,7 +16639,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A253" s="2">
         <v>2018</v>
       </c>
@@ -16660,7 +16681,7 @@
         <v>2.9950229617784081</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A254" s="2">
         <v>2019</v>
       </c>
@@ -16702,7 +16723,7 @@
         <v>2.9209999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A255" s="2">
         <v>2019</v>
       </c>
@@ -16744,7 +16765,7 @@
         <v>2.9689999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A256" s="2">
         <v>2019</v>
       </c>
@@ -16786,7 +16807,7 @@
         <v>2.9430000000000001</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A257" s="2">
         <v>2019</v>
       </c>
@@ -16828,7 +16849,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A258" s="2">
         <v>2019</v>
       </c>
@@ -16870,7 +16891,7 @@
         <v>3.121</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A259" s="2">
         <v>2019</v>
       </c>
@@ -16912,7 +16933,7 @@
         <v>3.2040000000000002</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A260" s="2">
         <v>2019</v>
       </c>
@@ -16954,7 +16975,7 @@
         <v>3.431</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A261" s="2">
         <v>2019</v>
       </c>
@@ -16996,7 +17017,7 @@
         <v>3.4119999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2">
         <v>2019</v>
       </c>
@@ -17038,7 +17059,7 @@
         <v>3.613</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A263" s="2">
         <v>2019</v>
       </c>
@@ -17080,7 +17101,7 @@
         <v>3.827</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A264" s="2">
         <v>2019</v>
       </c>
@@ -17122,7 +17143,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A265" s="2">
         <v>2019</v>
       </c>
@@ -17164,7 +17185,7 @@
         <v>3.9329999999999998</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A266" s="2">
         <v>2020</v>
       </c>
@@ -17206,7 +17227,7 @@
         <v>3.6349999999999998</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A267" s="2">
         <v>2020</v>
       </c>
@@ -17248,7 +17269,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A268" s="2">
         <v>2020</v>
       </c>
@@ -17290,7 +17311,7 @@
         <v>3.234</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A269" s="2">
         <v>2020</v>
       </c>
@@ -17332,7 +17353,7 @@
         <v>3.202</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A270" s="2">
         <v>2020</v>
       </c>
@@ -17374,7 +17395,7 @@
         <v>3.0590000000000002</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A271" s="2">
         <v>2020</v>
       </c>
@@ -17416,7 +17437,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A272" s="2">
         <v>2020</v>
       </c>
@@ -17458,7 +17479,7 @@
         <v>3.0859999999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A273" s="2">
         <v>2020</v>
       </c>
@@ -17500,7 +17521,7 @@
         <v>3.0609999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A274" s="2">
         <v>2020</v>
       </c>
@@ -17542,7 +17563,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A275" s="2">
         <v>2020</v>
       </c>
@@ -17584,7 +17605,7 @@
         <v>3.093</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A276" s="2">
         <v>2020</v>
       </c>
@@ -17626,7 +17647,7 @@
         <v>2.9820000000000002</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2">
         <v>2020</v>
       </c>
@@ -17668,7 +17689,7 @@
         <v>2.8410000000000002</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2">
         <v>2021</v>
       </c>
@@ -17709,7 +17730,7 @@
         <v>2.8530000000000002</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2">
         <v>2021</v>
       </c>
@@ -17751,7 +17772,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2">
         <v>2021</v>
       </c>
@@ -17793,7 +17814,7 @@
         <v>3.1920000000000002</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2">
         <v>2021</v>
       </c>
@@ -17835,7 +17856,7 @@
         <v>3.3559999999999999</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2">
         <v>2021</v>
       </c>
@@ -17877,7 +17898,7 @@
         <v>3.6019999999999999</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2">
         <v>2021</v>
       </c>
@@ -17919,7 +17940,7 @@
         <v>3.8460000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2">
         <v>2021</v>
       </c>
@@ -17961,7 +17982,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2">
         <v>2021</v>
       </c>
@@ -18003,7 +18024,7 @@
         <v>4.2069999999999999</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2">
         <v>2021</v>
       </c>
@@ -18045,7 +18066,7 @@
         <v>4.3579999999999997</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2">
         <v>2021</v>
       </c>
@@ -18087,7 +18108,7 @@
         <v>4.4829999999999997</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2">
         <v>2021</v>
       </c>
@@ -18129,7 +18150,7 @@
         <v>4.3630000000000004</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2">
         <v>2021</v>
       </c>
@@ -18171,7 +18192,7 @@
         <v>3.9740000000000002</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2">
         <v>2022</v>
       </c>
@@ -18213,7 +18234,7 @@
         <v>3.6070000000000002</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2">
         <v>2022</v>
       </c>
@@ -18255,7 +18276,7 @@
         <v>3.6589999999999998</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2">
         <v>2022</v>
       </c>
@@ -18297,7 +18318,7 @@
         <v>3.964</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2">
         <v>2022</v>
       </c>
@@ -18339,7 +18360,7 @@
         <v>4.0640000000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2">
         <v>2022</v>
       </c>
@@ -18378,7 +18399,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2">
         <v>2022</v>
       </c>
@@ -18417,7 +18438,7 @@
         <v>4.1920000000000002</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2">
         <v>2022</v>
       </c>
@@ -18456,7 +18477,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2">
         <v>2022</v>
       </c>
@@ -18495,7 +18516,7 @@
         <v>4.2949999999999999</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2">
         <v>2022</v>
       </c>
@@ -18534,7 +18555,7 @@
         <v>4.0940000000000003</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2">
         <v>2022</v>
       </c>
@@ -18573,7 +18594,7 @@
         <v>3.1629999999999998</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2">
         <v>2022</v>
       </c>
@@ -18612,7 +18633,7 @@
         <v>2.6560000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2">
         <v>2022</v>
       </c>
@@ -18651,7 +18672,7 @@
         <v>2.536</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2">
         <v>2023</v>
       </c>
@@ -18690,7 +18711,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2">
         <v>2023</v>
       </c>
@@ -18729,7 +18750,7 @@
         <v>2.7469999999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2">
         <v>2023</v>
       </c>
@@ -18768,7 +18789,7 @@
         <v>2.9980000000000002</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2">
         <v>2023</v>
       </c>
@@ -18807,7 +18828,7 @@
         <v>3.1240000000000001</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2">
         <v>2023</v>
       </c>
@@ -18846,7 +18867,7 @@
         <v>2.8090000000000002</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2">
         <v>2023</v>
       </c>
@@ -18885,7 +18906,7 @@
         <v>2.5579999999999998</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2">
         <v>2023</v>
       </c>
@@ -18924,7 +18945,7 @@
         <v>2.532</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2">
         <v>2023</v>
       </c>
@@ -18963,7 +18984,7 @@
         <v>2.3969999999999998</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2">
         <v>2023</v>
       </c>
@@ -19002,7 +19023,7 @@
         <v>2.4319999999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2">
         <v>2023</v>
       </c>
@@ -19041,7 +19062,7 @@
         <v>2.3809999999999998</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2">
         <v>2023</v>
       </c>
@@ -19080,7 +19101,7 @@
         <v>2.2029999999999998</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2">
         <v>2023</v>
       </c>
@@ -19119,7 +19140,7 @@
         <v>2.1920000000000002</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2">
         <v>2024</v>
       </c>
@@ -19158,7 +19179,7 @@
         <v>2.274</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2">
         <v>2024</v>
       </c>
@@ -19197,7 +19218,7 @@
         <v>2.4620000000000002</v>
       </c>
     </row>
-    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2">
         <v>2024</v>
       </c>
@@ -19236,7 +19257,7 @@
         <v>2.5350000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2">
         <v>2024</v>
       </c>
@@ -19275,7 +19296,7 @@
         <v>2.7410000000000001</v>
       </c>
     </row>
-    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2">
         <v>2024</v>
       </c>
@@ -19314,7 +19335,7 @@
         <v>2.7930000000000001</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2">
         <v>2024</v>
       </c>
@@ -19353,7 +19374,7 @@
         <v>2.9889999999999999</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2">
         <v>2024</v>
       </c>
@@ -19392,7 +19413,7 @@
         <v>3.1110000000000002</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2">
         <v>2024</v>
       </c>
@@ -19431,7 +19452,7 @@
         <v>3.1850000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2">
         <v>2024</v>
       </c>
@@ -19470,7 +19491,7 @@
         <v>3.1419999999999999</v>
       </c>
     </row>
-    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2">
         <v>2024</v>
       </c>
@@ -19509,7 +19530,7 @@
         <v>3.2509999999999999</v>
       </c>
     </row>
-    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2">
         <v>2024</v>
       </c>
@@ -19548,7 +19569,7 @@
         <v>3.2970000000000002</v>
       </c>
     </row>
-    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2">
         <v>2024</v>
       </c>
@@ -19587,7 +19608,7 @@
         <v>3.2309999999999999</v>
       </c>
     </row>
-    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2">
         <v>2025</v>
       </c>
@@ -19626,7 +19647,7 @@
         <v>3.3580000000000001</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2">
         <v>2025</v>
       </c>
@@ -19665,7 +19686,7 @@
         <v>3.2989999999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2">
         <v>2025</v>
       </c>
@@ -19704,7 +19725,7 @@
         <v>3.5249999999999999</v>
       </c>
     </row>
-    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2">
         <v>2025</v>
       </c>
@@ -19743,7 +19764,7 @@
         <v>3.496</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2">
         <v>2025</v>
       </c>
@@ -19782,7 +19803,7 @@
         <v>3.5640000000000001</v>
       </c>
     </row>
-    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2">
         <v>2025</v>
       </c>
@@ -19821,7 +19842,7 @@
         <v>3.6320000000000001</v>
       </c>
     </row>
-    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2">
         <v>2025</v>
       </c>
@@ -19860,7 +19881,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2">
         <v>2025</v>
       </c>
@@ -19899,7 +19920,7 @@
         <v>4.3029999999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2">
         <v>2025</v>
       </c>
@@ -19938,7 +19959,7 @@
         <v>4.4409999999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2">
         <v>2025</v>
       </c>
@@ -19977,7 +19998,7 @@
         <v>4.7690000000000001</v>
       </c>
     </row>
-    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2">
         <v>2025</v>
       </c>
@@ -20016,7 +20037,7 @@
         <v>4.8339999999999996</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2">
         <v>2025</v>
       </c>
@@ -20055,7 +20076,7 @@
         <v>4.6840000000000002</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2">
         <v>2026</v>
       </c>
@@ -20094,7 +20115,7 @@
         <v>4.6260000000000003</v>
       </c>
     </row>
-    <row r="339" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2">
         <v>2026</v>
       </c>
@@ -20133,7 +20154,7 @@
         <v>4.7889999999999997</v>
       </c>
     </row>
-    <row r="340" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2">
         <v>2026</v>
       </c>
@@ -20172,7 +20193,7 @@
         <v>4.8490000000000002</v>
       </c>
     </row>
-    <row r="341" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2">
         <v>2026</v>
       </c>
@@ -20211,7 +20232,7 @@
         <v>4.8470000000000004</v>
       </c>
     </row>
-    <row r="342" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2">
         <v>2026</v>
       </c>
@@ -20250,7 +20271,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="343" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="2">
         <v>2026</v>
       </c>
@@ -20287,6 +20308,45 @@
       </c>
       <c r="M343" s="3">
         <v>5.0919999999999996</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A344" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B344" s="18"/>
+      <c r="C344" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D344" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="E344" s="3">
+        <v>5.851</v>
+      </c>
+      <c r="F344" s="3">
+        <v>5.7640000000000002</v>
+      </c>
+      <c r="G344" s="1">
+        <v>2.7450000000000001</v>
+      </c>
+      <c r="H344" s="3">
+        <v>5.3369999999999997</v>
+      </c>
+      <c r="I344" s="1">
+        <v>3.181</v>
+      </c>
+      <c r="J344" s="3">
+        <v>5.7880000000000003</v>
+      </c>
+      <c r="K344" s="3">
+        <v>5.6180000000000003</v>
+      </c>
+      <c r="L344" s="3">
+        <v>6.2670000000000003</v>
+      </c>
+      <c r="M344" s="3">
+        <v>5.1100000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -20297,6 +20357,7 @@
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="I10:J10"/>
   </mergeCells>
+  <phoneticPr fontId="34" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" r:id="rId1"/>
   <drawing r:id="rId2"/>
